--- a/PCBNo.10081/FPGA/修正履歴.xlsx
+++ b/PCBNo.10081/FPGA/修正履歴.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/512e22ffcc52695f/ドキュメント/GitHub/PCBNo.10081/PCBNo.10081/PCBNo.10081/SP0557_rev02_00_AI3/SP0557_rev02_00_AI3_2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/512e22ffcc52695f/ドキュメント/GitHub/PCBNo.10081/PCBNo.10081/FPGA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{BCDA7BAB-8026-4C53-BAA1-6CFCABC79B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41E34AB5-8F88-49EF-A593-73BDE1461DFE}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{BCDA7BAB-8026-4C53-BAA1-6CFCABC79B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74324252-AD45-4920-A6B2-E6EB76FC6AC7}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28320" firstSheet="1" activeTab="7" xr2:uid="{3A2BB469-6CC5-41C3-8C98-63503D4CF60C}"/>
+    <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28320" firstSheet="2" activeTab="8" xr2:uid="{3A2BB469-6CC5-41C3-8C98-63503D4CF60C}"/>
   </bookViews>
   <sheets>
     <sheet name="修正履歴" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="No5" sheetId="7" r:id="rId6"/>
     <sheet name="No6" sheetId="8" r:id="rId7"/>
     <sheet name="No.7" sheetId="9" r:id="rId8"/>
+    <sheet name="No.8" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="752">
   <si>
     <t>No</t>
     <phoneticPr fontId="1"/>
@@ -5133,12 +5134,457 @@
   <si>
     <t>CLKCOM_OUT→CLK2（open接続のため不存在）、/CLK2A→.CLK2A（区切り文字統一）</t>
   </si>
+  <si>
+    <t>08</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自宅PCでワーニングが増える原因を解消</t>
+    <rPh sb="0" eb="2">
+      <t>ジタク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ゲンイン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カイショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Synplifyが自動でクロック制約を生成する設定になっている。自動生成の結果が間違っている。</t>
+  </si>
+  <si>
+    <t>実際の周期</t>
+  </si>
+  <si>
+    <t>自動生成の周期</t>
+  </si>
+  <si>
+    <t>倍率</t>
+  </si>
+  <si>
+    <t>CLKOS2 (20MHz)</t>
+  </si>
+  <si>
+    <t>50ns</t>
+  </si>
+  <si>
+    <t>6.2ns</t>
+  </si>
+  <si>
+    <t>8倍タイト</t>
+  </si>
+  <si>
+    <t>CLK20M (20MHz)</t>
+  </si>
+  <si>
+    <t>2.6ns</t>
+  </si>
+  <si>
+    <t>19倍タイト</t>
+  </si>
+  <si>
+    <t>CLKOS (100MHz)</t>
+  </si>
+  <si>
+    <t>10ns</t>
+  </si>
+  <si>
+    <t>4倍タイト</t>
+  </si>
+  <si>
+    <t>CLKOP (100MHz)</t>
+  </si>
+  <si>
+    <t>3.5ns</t>
+  </si>
+  <si>
+    <t>3倍タイト</t>
+  </si>
+  <si>
+    <t>CLKOS3 (10MHz)</t>
+  </si>
+  <si>
+    <t>100ns</t>
+  </si>
+  <si>
+    <t>定義漏れ</t>
+  </si>
+  <si>
+    <t>なぜ15,037件になるか</t>
+  </si>
+  <si>
+    <t>pll_gen.fdc が空 → SP0557.fdc のネット名が間違い（全無視）</t>
+  </si>
+  <si>
+    <t>→ frequency auto で AutoConstraint_SP0557.sdc を使用</t>
+  </si>
+  <si>
+    <t>→ 周期が3〜19倍タイト + 別clockgroup</t>
+  </si>
+  <si>
+    <t>→ 9,600個のFF × 6クロックドメインのほぼ全パスがタイミング違反</t>
+  </si>
+  <si>
+    <t>→ 各違反パスにワーニング出力 → 15,037件</t>
+  </si>
+  <si>
+    <t>なぜ職場PCでは16件だったか</t>
+  </si>
+  <si>
+    <r>
+      <t>1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>SP0557_syn.prj</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.5"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>frequency auto</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.5"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> (自動制約モード)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>AutoConstraint_SP0557.sdc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.5"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: クロック周期が大幅に間違い</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>さらに各クロックが</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>別々のclockgroup</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>に配置 → クロスドメイン解析が不正確</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>SP0557.fdc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.5"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: ネット名が間違い → Synplifyが全制約をサイレントに無視</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>{n:slv_com_top_inst.clk_gen_inst2.PLL_inst.CLKCOM_OUT}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> 等の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>存在しないネット名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>で参照しているため、正しい制約が書かれていても全て無視される。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>pll_gen.fdc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.5"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: 空ファイル（IPコアのスタブのみ）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>職場PCは </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>C:\work\S127M\PCBNo_10081\SP0557_rev02_00_AI3\</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> でgitとは</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>別の独立コピー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>。そちらでは</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>.prj</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>や制約ファイルが正しく設定されていた（手動修正またはSynplifyキャッシュによる）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>既にコミット </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>22fa5be</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> で修正済み（このブランチに含まれている）:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>frequency auto</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>100.0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>pll_gen.fdc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> に正しいPLLポート名 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>{p:CLKOP}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> 等でクロック定義追加</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SP0557.fdc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> を pll_gen.fdc のクロック名を参照する形にリライト</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>AutoConstraint_SP0557.sdc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> を無効化</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>家PCでの復旧手順</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: このブランチをmasterにマージ → Diamond でClean → Synthesize Design → 16件に戻るはず。</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="27">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5333,6 +5779,24 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="13.5"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -5398,7 +5862,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5643,6 +6107,24 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6092,9 +6574,15 @@
       <c r="F11" s="26"/>
     </row>
     <row r="12" spans="3:6">
-      <c r="C12" s="26"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="27"/>
+      <c r="C12" s="26">
+        <v>8</v>
+      </c>
+      <c r="D12" s="29" t="s">
+        <v>710</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>711</v>
+      </c>
       <c r="F12" s="26"/>
     </row>
     <row r="13" spans="3:6">
@@ -10263,4 +10751,219 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1C504B7-EEB2-42BE-916D-0045C563FE42}">
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="1" width="70.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="28"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="18.75">
+      <c r="A1" s="82" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="9" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="18.75">
+      <c r="A3" s="82" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="31.5">
+      <c r="A4" s="83" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="83" t="s">
+        <v>713</v>
+      </c>
+      <c r="C4" s="83" t="s">
+        <v>714</v>
+      </c>
+      <c r="D4" s="84" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="16.5" thickBot="1">
+      <c r="A5" s="7" t="s">
+        <v>716</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>717</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>718</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="32.25" thickBot="1">
+      <c r="A6" s="7" t="s">
+        <v>720</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>717</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>721</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="16.5" thickBot="1">
+      <c r="A7" s="7" t="s">
+        <v>723</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>721</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="16.5" thickBot="1">
+      <c r="A8" s="7" t="s">
+        <v>726</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>727</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="7" t="s">
+        <v>729</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>730</v>
+      </c>
+      <c r="C9" s="85" t="s">
+        <v>731</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="9" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="18.75">
+      <c r="A11" s="82" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="31.5">
+      <c r="A12" s="21" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="18.75">
+      <c r="A13" s="82" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="18.75">
+      <c r="A15" s="82" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="1" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="18.75">
+      <c r="A21" s="82" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="47.25">
+      <c r="A22" s="9" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="18.75">
+      <c r="A23" s="82" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="9" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="11"/>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="86" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="86" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="86" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="86" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="31.5">
+      <c r="A31" s="87" t="s">
+        <v>751</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/PCBNo.10081/FPGA/修正履歴.xlsx
+++ b/PCBNo.10081/FPGA/修正履歴.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/512e22ffcc52695f/ドキュメント/GitHub/PCBNo.10081/PCBNo.10081/FPGA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{BCDA7BAB-8026-4C53-BAA1-6CFCABC79B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74324252-AD45-4920-A6B2-E6EB76FC6AC7}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{BCDA7BAB-8026-4C53-BAA1-6CFCABC79B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9DB8534-7D9A-49AF-85EB-704BE2F56C5F}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28320" firstSheet="2" activeTab="8" xr2:uid="{3A2BB469-6CC5-41C3-8C98-63503D4CF60C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="9" xr2:uid="{3A2BB469-6CC5-41C3-8C98-63503D4CF60C}"/>
   </bookViews>
   <sheets>
     <sheet name="修正履歴" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="No6" sheetId="8" r:id="rId7"/>
     <sheet name="No.7" sheetId="9" r:id="rId8"/>
     <sheet name="No.8" sheetId="10" r:id="rId9"/>
+    <sheet name="No.9" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="836">
   <si>
     <t>No</t>
     <phoneticPr fontId="1"/>
@@ -5577,6 +5578,657 @@
         <charset val="128"/>
       </rPr>
       <t>: このブランチをmasterにマージ → Diamond でClean → Synthesize Design → 16件に戻るはず。</t>
+    </r>
+  </si>
+  <si>
+    <t>09_1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>No1~8が適応できているかの確認</t>
+    <rPh sb="6" eb="8">
+      <t>テキオウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>修正履歴No.1〜No.8の適用確認を行った結果、コードレベルでは全修正が適用済みだが、コンパイル結果に以下4つの残存問題がある。本計画でこれら全てを修正する。</t>
+  </si>
+  <si>
+    <t>修正1: CD134 識別子エラー修正（3件）</t>
+  </si>
+  <si>
+    <t>原因</t>
+  </si>
+  <si>
+    <t>変更前:</t>
+  </si>
+  <si>
+    <t>変更後:</t>
+  </si>
+  <si>
+    <t>-- ENB_START preservation handled by SP0557.fdc (Section 7N)</t>
+  </si>
+  <si>
+    <t>-- DATAOUT preservation handled by SP0557.fdc (Section 7E)</t>
+  </si>
+  <si>
+    <t>-- NODE preservation handled by SP0557.fdc (Section 7D)</t>
+  </si>
+  <si>
+    <t>### 原因</t>
+  </si>
+  <si>
+    <t>### 修正内容</t>
+  </si>
+  <si>
+    <t>修正4: SLICE使用率改善</t>
+  </si>
+  <si>
+    <t>対応方針</t>
+  </si>
+  <si>
+    <t>修正3の115MHz→100MHz変更により、以下の改善が期待される:</t>
+  </si>
+  <si>
+    <t>Synplifyのレジスタ複製削減（タイミング圧力緩和）</t>
+  </si>
+  <si>
+    <t>P&amp;Rの配置最適化余地拡大</t>
+  </si>
+  <si>
+    <t>推定効果: 89% → 85-87%程度</t>
+  </si>
+  <si>
+    <t>追加のRTL変更は行わない（修正2のFDCクロック定義が正しく適用されれば、合成最適化の質も改善される）。</t>
+  </si>
+  <si>
+    <t>修正対象ファイル一覧</t>
+  </si>
+  <si>
+    <t>RTL/SP0557/compactppmc/ppmc_ctrl.vhd</t>
+  </si>
+  <si>
+    <t>ENB_START属性削除</t>
+  </si>
+  <si>
+    <t>RTL/SP0557/slv_com/rx_com/dec6b_5b.vhd</t>
+  </si>
+  <si>
+    <t>DATAOUT属性削除</t>
+  </si>
+  <si>
+    <t>RTL/SP0557/slv_com/slv_ctrl/slv_rx_ctrl.vhd</t>
+  </si>
+  <si>
+    <t>NODE属性削除</t>
+  </si>
+  <si>
+    <t>RTL/IPcore/pll_gen/pll_gen.fdc</t>
+  </si>
+  <si>
+    <t>FPGA/SP0557.lpf</t>
+  </si>
+  <si>
+    <t>115MHz → 100MHz</t>
+  </si>
+  <si>
+    <t>修正適用後、Lattice Diamond / Synplifyでフルビルドを実施し、以下を確認:</t>
+  </si>
+  <si>
+    <t>BN137, MO160, MO129, CL177, CL240, CD638 が消滅したままであること</t>
+  </si>
+  <si>
+    <t>全クロックドメインの制約がPASSすること（CLKCOM_OUT含む）</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">RTLソースファイル内で </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>attribute syn_preserve of XXXX : signal is true;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> と記述しているが、対象がエンティティの</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>出力ポート</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>であるため、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: signal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> ではなく </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: port</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> を使う必要がある。FDCファイル(SP0557.fdc)には既に正しい制約が定義されているため、RTL内の重複属性を削除するのが最もクリーン。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ファイル1: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>PCBNo.10081/FPGA/RTL/SP0557/compactppmc/ppmc_ctrl.vhd</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> (133-136行)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">削除: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ENB_START</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> のsyn_preserve属性宣言（ENB_STARTは出力ポート）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>s_pls_ld</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> は内部signal なので残す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SP0557.fdc 7N節（246行: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>define_attribute {v:work.ppmc_ctrl} syn_preserve {1}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>）がモジュール全体を保護しているため、RTL属性は不要</t>
+    </r>
+  </si>
+  <si>
+    <t>attribute syn_preserve : boolean;</t>
+  </si>
+  <si>
+    <t>attribute syn_preserve of s_pls_ld  : signal is true;</t>
+  </si>
+  <si>
+    <t>attribute syn_preserve of ENB_START : signal is true;</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ファイル2: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>PCBNo.10081/FPGA/RTL/SP0557/slv_com/rx_com/dec6b_5b.vhd</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> (36-38行)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">削除: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>DATAOUT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> のsyn_preserve属性宣言（DATAOUTは出力ポート）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SP0557.fdc 7E節（166-171行）が合成後レジスタ名 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>DATAOUT_33_0_areg[*]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> で保護済み</t>
+    </r>
+  </si>
+  <si>
+    <t>attribute syn_preserve of DATAOUT : signal is true;</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ファイル3: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>PCBNo.10081/FPGA/RTL/SP0557/slv_com/slv_ctrl/slv_rx_ctrl.vhd</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> (90-94行)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">削除: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>NODE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> のsyn_preserve属性宣言（NODEは出力ポート）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>byte_cnt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> はinternal signal なので残す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SP0557.fdc 7D節（159-162行）が </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>NODE[0:3]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> を階層パス付きで保護済み</t>
+    </r>
+  </si>
+  <si>
+    <t>attribute syn_keep : boolean;</t>
+  </si>
+  <si>
+    <t>attribute syn_keep of byte_cnt : signal is true;</t>
+  </si>
+  <si>
+    <t>attribute syn_preserve of NODE : signal is true;</t>
+  </si>
+  <si>
+    <t>## 修正2: MT420/MT529 警告修正（10件）</t>
+  </si>
+  <si>
+    <t>`pll_gen.fdc` で `{p:CLKOP}` 等のポート参照構文を使用しているが、Synplifyは内部信号 `CLKOP_t` からクロックを推論し、`pll_gen|CLKOP_inferred_clock` という名前を生成する。FDCのポート参照と推論クロック名が一致しないため、FDCのdefine_clockが**黙殺**されている。</t>
+  </si>
+  <si>
+    <t>結果として全PLLクロックが `set_option -frequency 100.0` の10ns周期（100MHz）で処理され、実際の周波数と一致しないクロック（CLKOS2=20MHz, CLKOS3=10MHz）で不正確な合成最適化が行われている。</t>
+  </si>
+  <si>
+    <t>**ファイル: `PCBNo.10081/FPGA/RTL/IPcore/pll_gen/pll_gen.fdc`**</t>
+  </si>
+  <si>
+    <t>`{p:PORT}` 構文を `{n:SIGNAL}` 構文に変更し、Synplifyが実際に推論する内部信号名を参照する。</t>
+  </si>
+  <si>
+    <t>define_clock -name {CLKOP_100M} {p:CLKOP} -freq 100.000 ...</t>
+  </si>
+  <si>
+    <t>define_clock -name {CLKOS_100M_90} {p:CLKOS} -freq 100.000 ...</t>
+  </si>
+  <si>
+    <t>define_clock -name {CLKOS2_20M} {p:CLKOS2} -freq 20.000 ...</t>
+  </si>
+  <si>
+    <t>define_clock -name {CLKOS3_10M} {p:CLKOS3} -freq 10.000 ...</t>
+  </si>
+  <si>
+    <t>define_clock -name {CLKOP_100M} {n:CLKOP_t} -freq 100.000 ...</t>
+  </si>
+  <si>
+    <t>define_clock -name {CLKOS_100M_90} {n:CLKOS_t} -freq 100.000 ...</t>
+  </si>
+  <si>
+    <t>define_clock -name {CLKOS2_20M} {n:CLKOS2_t} -freq 20.000 ...</t>
+  </si>
+  <si>
+    <t>define_clock -name {CLKOS3_10M} {n:CLKOS3_t} -freq 10.000 ...</t>
+  </si>
+  <si>
+    <t>`CLKOP_t`, `CLKOS_t`, `CLKOS2_t`, `CLKOS3_t` は `pll_gen.vhd` の23-30行で宣言された内部信号で、EHXPLLLプリミティブの出力に直接接続されている（79-80行）。</t>
+  </si>
+  <si>
+    <t>**注意**: `{n:SIGNAL}` が効かない場合のフォールバックとして、EHXPLLLインスタンスの出力ピンを直接参照する構文も検討:</t>
+  </si>
+  <si>
+    <t>define_clock -name {CLKOP_100M} {n:PLLInst_0.CLKOP} -freq 100.000 ...</t>
+  </si>
+  <si>
+    <t>## 修正3: CLKCOM_OUT タイミング違反修正</t>
+  </si>
+  <si>
+    <t>LPFで100MHzクロックに115MHzのガードバンド制約を設定しているが、DCFIFO Block RAM出力→TX制御レジスタのクリティカルパスが9.823ns（C2Q: 5.830ns + routing: 2.874ns + LUT: 0.236ns）で、8.696ns（115MHz）の制約を1.275ns超過している。</t>
+  </si>
+  <si>
+    <t>100MHz（10ns周期）なら9.852nsの余裕があり、マージナルだがPASSする。</t>
+  </si>
+  <si>
+    <t>**ファイル: `PCBNo.10081/FPGA/SP0557.lpf` (303-304行)**</t>
+  </si>
+  <si>
+    <t>FREQUENCY NET "slv_com_top_inst.CLK2" 115.000000 MHz ;</t>
+  </si>
+  <si>
+    <t>FREQUENCY NET "slv_com_top_inst.CLK2A" 115.000000 MHz ;</t>
+  </si>
+  <si>
+    <t>FREQUENCY NET "slv_com_top_inst.CLK2" 100.000000 MHz ;</t>
+  </si>
+  <si>
+    <t>FREQUENCY NET "slv_com_top_inst.CLK2A" 100.000000 MHz ;</t>
+  </si>
+  <si>
+    <r>
+      <t>LPFコメント更新</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: Section 1のガードバンドに関するコメント（299行）を更新し、115MHz→100MHzに戻した理由を記載</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>{p:PORT}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>{n:SIGNAL_t}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. CD134エラー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: 3件 → 0件になること</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. MT420/MT529警告</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: 10件 → 0件（または大幅減少）になること</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>{n:SIGNAL_t}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> が効かない場合は代替構文を試行</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. CLKCOM_OUT制約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: 100MHz制約でsetup/hold共にPASSすること</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4. Hold違反</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: 4件 → 0件になること（115MHz緩和による改善）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>5. SLICE使用率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: 89%から低下していること</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>6. 既存の修正が壊れていないこと</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>:</t>
     </r>
   </si>
 </sst>
@@ -5786,13 +6438,14 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Meiryo UI"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="10"/>
       <name val="Meiryo UI"/>
       <family val="3"/>
       <charset val="128"/>
@@ -5862,7 +6515,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6112,20 +6765,23 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6586,9 +7242,15 @@
       <c r="F12" s="26"/>
     </row>
     <row r="13" spans="3:6">
-      <c r="C13" s="26"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="27"/>
+      <c r="C13" s="26">
+        <v>9</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>752</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>753</v>
+      </c>
       <c r="F13" s="26"/>
     </row>
     <row r="14" spans="3:6">
@@ -6704,6 +7366,628 @@
       <c r="D32" s="29"/>
       <c r="E32" s="27"/>
       <c r="F32" s="26"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14089E9A-DD6C-474E-BC76-1DCDCF7A2A9D}">
+  <dimension ref="A1:B181"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="24">
+      <c r="A1" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="24">
+      <c r="A7" s="14" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="18.75">
+      <c r="A9" s="15" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="18.75">
+      <c r="A13" s="15" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="17" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="18"/>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="18" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="24" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="18" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="16" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="16" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="16" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="1" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="16" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="16" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="16" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="17" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="18"/>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="18" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="18" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="16" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="16" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="1" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="16" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="17" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="18"/>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="18" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="24" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="18" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="1" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="16" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="16" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="16" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="16" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="1" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="16" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="16" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="16" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="16" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="16" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="16" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="16" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="16" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="16" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="16" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="16" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="16" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="16" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="16" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="16" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="16" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="16" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="16" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="16" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="16" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="16" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="16" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="16" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="16" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="16" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="16" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="16" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="16" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="16" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="16" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="16" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="16" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="16" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="16" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="16" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="16" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="16" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" s="16" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="16" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="16" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="16" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" s="16" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" s="16" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" s="16" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" s="16" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" s="16" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="16" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" s="17" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" ht="24">
+      <c r="A145" s="14" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" ht="18.75">
+      <c r="A147" s="15" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="1" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" s="18"/>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" s="18" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" s="18" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" s="18" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" s="1" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" ht="24">
+      <c r="A159" s="14" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="B161" s="20" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" ht="71.25">
+      <c r="A162" s="21" t="s">
+        <v>772</v>
+      </c>
+      <c r="B162" s="9" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" ht="71.25">
+      <c r="A163" s="21" t="s">
+        <v>774</v>
+      </c>
+      <c r="B163" s="9" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" ht="71.25">
+      <c r="A164" s="21" t="s">
+        <v>776</v>
+      </c>
+      <c r="B164" s="9" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" ht="60">
+      <c r="A165" s="21" t="s">
+        <v>778</v>
+      </c>
+      <c r="B165" s="21" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" ht="47.25">
+      <c r="A166" s="21" t="s">
+        <v>779</v>
+      </c>
+      <c r="B166" s="9" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" ht="24">
+      <c r="A169" s="14" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="1" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="18"/>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="19" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="19" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="88" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="19" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" s="19" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" s="19" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" s="19" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" s="25" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" s="25" t="s">
+        <v>783</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/PCBNo.10081/FPGA/修正履歴.xlsx
+++ b/PCBNo.10081/FPGA/修正履歴.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/512e22ffcc52695f/ドキュメント/GitHub/PCBNo.10081/PCBNo.10081/FPGA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{BCDA7BAB-8026-4C53-BAA1-6CFCABC79B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9DB8534-7D9A-49AF-85EB-704BE2F56C5F}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:1_{BCDA7BAB-8026-4C53-BAA1-6CFCABC79B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31106169-8E09-4C80-B0B7-3F21D16E9761}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="9" xr2:uid="{3A2BB469-6CC5-41C3-8C98-63503D4CF60C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="10" xr2:uid="{3A2BB469-6CC5-41C3-8C98-63503D4CF60C}"/>
   </bookViews>
   <sheets>
     <sheet name="修正履歴" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="No.7" sheetId="9" r:id="rId8"/>
     <sheet name="No.8" sheetId="10" r:id="rId9"/>
     <sheet name="No.9" sheetId="11" r:id="rId10"/>
+    <sheet name="No.10" sheetId="12" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="836">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="1019">
   <si>
     <t>No</t>
     <phoneticPr fontId="1"/>
@@ -6231,12 +6232,992 @@
       <t>:</t>
     </r>
   </si>
+  <si>
+    <t>10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>No1~9の確認</t>
+    <rPh sb="6" eb="8">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FDCファイルがDiamondプロジェクトに未登録</t>
+  </si>
+  <si>
+    <t>修正履歴 No.1〜9 コンパイル結果検証レポート</t>
+  </si>
+  <si>
+    <t>コンパイル日時: 2026-02-28 (SP0557_SP0557.srr / SP0557_SP0557.twr)</t>
+  </si>
+  <si>
+    <t>全体結果サマリ</t>
+  </si>
+  <si>
+    <t>区分</t>
+  </si>
+  <si>
+    <t>コンパイルエラー</t>
+  </si>
+  <si>
+    <t>Setupタイミング違反</t>
+  </si>
+  <si>
+    <t>Holdタイミング違反</t>
+  </si>
+  <si>
+    <t>合成ワーニング</t>
+  </si>
+  <si>
+    <t>272件</t>
+  </si>
+  <si>
+    <t>修正No.9で計画した4つの修正の適用状況</t>
+  </si>
+  <si>
+    <t>修正1: CD134 識別子エラー修正（3件） → 適用済み・効果あり</t>
+  </si>
+  <si>
+    <t>ソース状態</t>
+  </si>
+  <si>
+    <t>コンパイル反映</t>
+  </si>
+  <si>
+    <t>ppmc_ctrl.vhd:133-136</t>
+  </si>
+  <si>
+    <t>ENB_START syn_preserve削除</t>
+  </si>
+  <si>
+    <t>適用済み</t>
+  </si>
+  <si>
+    <t>dec6b_5b.vhd:36-37</t>
+  </si>
+  <si>
+    <t>DATAOUT syn_preserve削除</t>
+  </si>
+  <si>
+    <t>slv_rx_ctrl.vhd:90-93</t>
+  </si>
+  <si>
+    <t>NODE syn_preserve削除</t>
+  </si>
+  <si>
+    <t>s_pls_ld / byte_cnt の属性も正しく保持されています。</t>
+  </si>
+  <si>
+    <t>修正2: MT420/MT529 PLL クロック制約修正 → ソース適用済みだがコンパイル未反映（致命的）</t>
+  </si>
+  <si>
+    <t>問題: FDCファイルがSynplifyに読み込まれていない</t>
+  </si>
+  <si>
+    <t>合成レポート 1240行目:</t>
+  </si>
+  <si>
+    <t>@A: MF827 |No constraint file specified.</t>
+  </si>
+  <si>
+    <t>Removed file: C:\FPGA work\PCBNo.10081\FPGA\RTL\IPcore\pll_gen\pll_gen.fdc</t>
+  </si>
+  <si>
+    <t>Removed file: C:\FPGA work\PCBNo.10081\FPGA\SP0557\SP0557.fdc</t>
+  </si>
+  <si>
+    <t>@W: MT420 |Found inferred clock pll_gen|CLKOS2_inferred_clock with period 5.00ns</t>
+  </si>
+  <si>
+    <t>@W: MT420 |Found inferred clock SP0557|CLK20M with period 5.00ns</t>
+  </si>
+  <si>
+    <t>@W: MT420 |Found inferred clock pll_gen|CLKOS_inferred_clock with period 5.00ns</t>
+  </si>
+  <si>
+    <t>@W: MT420 |Found inferred clock pll_gen|CLKOP_inferred_clock with period 5.00ns</t>
+  </si>
+  <si>
+    <t>@W: MT420 |Found inferred clock pll_gen|CLKOS3_inferred_clock with period 5.00ns</t>
+  </si>
+  <si>
+    <t>全PLLクロックがデフォルト200MHz (5ns)として推定され、FDCのclock group/multicycle/false path制約も全て無効です。</t>
+  </si>
+  <si>
+    <t>修正3: CLKCOM_OUT タイミング違反修正 → 一部適用だが主要制約が未反映（致命的）</t>
+  </si>
+  <si>
+    <t>UP_TXD SLEWRATE=FAST</t>
+  </si>
+  <si>
+    <t>FREQUENCY PORT "UP_CLK" 20MHz</t>
+  </si>
+  <si>
+    <t>FREQUENCY NET制約 (5クロック)</t>
+  </si>
+  <si>
+    <t>適用済み・反映あり</t>
+  </si>
+  <si>
+    <t>BLOCK PATH CLK20M_c &lt;-&gt; s_PLL_CLK20M/CLK1</t>
+  </si>
+  <si>
+    <t>MULTICYCLE s_PLL_CLK20M &lt;-&gt; CLK1 (2X)</t>
+  </si>
+  <si>
+    <t>問題: LPFのクロックネット名が実際のPAR認識名と不一致</t>
+  </si>
+  <si>
+    <t>LPF記述</t>
+  </si>
+  <si>
+    <t>PARが認識する実際のネット名</t>
+  </si>
+  <si>
+    <t>slv_com_top_inst.CLK2</t>
+  </si>
+  <si>
+    <t>slv_com_top_inst.CLKCOM_OUT</t>
+  </si>
+  <si>
+    <t>不一致</t>
+  </si>
+  <si>
+    <t>slv_com_top_inst.CLK2A</t>
+  </si>
+  <si>
+    <t>LPF Section</t>
+  </si>
+  <si>
+    <t>制約</t>
+  </si>
+  <si>
+    <t>影響</t>
+  </si>
+  <si>
+    <t>Section 2 (一部)</t>
+  </si>
+  <si>
+    <t>BLOCK PATH CLK20M_c &lt;-&gt; CLK2/CLK2A</t>
+  </si>
+  <si>
+    <t>CLK20M_c→CLKCOM_OUT/CLK2Aパスが解析対象に残存</t>
+  </si>
+  <si>
+    <t>Section 4</t>
+  </si>
+  <si>
+    <t>BLOCK PATH s_PLL_CLK20M &lt;-&gt; CLK2/CLK2A</t>
+  </si>
+  <si>
+    <t>20MHz↔100MHzパスが未遮断</t>
+  </si>
+  <si>
+    <t>Section 5</t>
+  </si>
+  <si>
+    <t>MULTICYCLE CLK1 &lt;-&gt; CLK2 (10X/2X)</t>
+  </si>
+  <si>
+    <t>59パスが100MHz解析下に残存（最大の問題）</t>
+  </si>
+  <si>
+    <t>Section 6</t>
+  </si>
+  <si>
+    <t>MULTICYCLE CLK1 &lt;-&gt; CLK2A (10X/2X)</t>
+  </si>
+  <si>
+    <t>CLK1↔CLK2Aパスが緩和されず</t>
+  </si>
+  <si>
+    <t>TWR（タイミングレポート）で確認した証拠:</t>
+  </si>
+  <si>
+    <t>タイミング結果詳細 (TWR)</t>
+  </si>
+  <si>
+    <t>クロックドメイン</t>
+  </si>
+  <si>
+    <t>実測</t>
+  </si>
+  <si>
+    <t>スラック</t>
+  </si>
+  <si>
+    <t>100.000 MHz</t>
+  </si>
+  <si>
+    <t>98.483 MHz</t>
+  </si>
+  <si>
+    <t>-0.154ns</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>CLK2A (100MHz)</t>
+  </si>
+  <si>
+    <t>271.370 MHz</t>
+  </si>
+  <si>
+    <t>+6.315ns</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>20.000 MHz</t>
+  </si>
+  <si>
+    <t>67.645 MHz</t>
+  </si>
+  <si>
+    <t>充分</t>
+  </si>
+  <si>
+    <t>CLK1 (10MHz)</t>
+  </si>
+  <si>
+    <t>10.000 MHz</t>
+  </si>
+  <si>
+    <t>14.067 MHz</t>
+  </si>
+  <si>
+    <t>UP_CLK_c (20MHz)</t>
+  </si>
+  <si>
+    <t>(パスなし)</t>
+  </si>
+  <si>
+    <t>必要な修正アクション</t>
+  </si>
+  <si>
+    <t>アクション1 (最優先): SP0557.ldfにFDCファイルを登録</t>
+  </si>
+  <si>
+    <t>これにより:</t>
+  </si>
+  <si>
+    <t>MT420/MT529ワーニングが解消</t>
+  </si>
+  <si>
+    <t>PLLクロックが正しい周波数で合成最適化される</t>
+  </si>
+  <si>
+    <t>FDCのmulticycle/false path制約がSynplify合成時に有効化される</t>
+  </si>
+  <si>
+    <t>アクション2 (最優先): LPFクロックネット名の修正</t>
+  </si>
+  <si>
+    <t># 修正前                                    # 修正後</t>
+  </si>
+  <si>
+    <t>"slv_com_top_inst.CLK2"                  → "slv_com_top_inst.CLKCOM_OUT"</t>
+  </si>
+  <si>
+    <t>"slv_com_top_inst.CLK2A"                 → "slv_com_top_inst/CLK2A"</t>
+  </si>
+  <si>
+    <t>LPF Section 2, 4, 5, 6 の全8箇所を修正する必要があります。</t>
+  </si>
+  <si>
+    <t>CLK1↔CLKCOM_OUT の59+23パスにMULTICYCLE制約が適用</t>
+  </si>
+  <si>
+    <t>CLKCOM_OUTのタイミング違反が解消される可能性が高い（ルーティング資源の解放）</t>
+  </si>
+  <si>
+    <t>まとめ</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>RTLソース</t>
+  </si>
+  <si>
+    <t>タイミング制約新規作成 (LPF)</t>
+  </si>
+  <si>
+    <t>✓ 適用済み</t>
+  </si>
+  <si>
+    <t>S3IO CLK制約追加 (LPF)</t>
+  </si>
+  <si>
+    <t>RTLデッドコード削除</t>
+  </si>
+  <si>
+    <t>✓ 反映済み</t>
+  </si>
+  <si>
+    <t>(No1-3分析)</t>
+  </si>
+  <si>
+    <t>ワーニング削除 (RTL+FDC)</t>
+  </si>
+  <si>
+    <t>FDC未読込のため一部未反映</t>
+  </si>
+  <si>
+    <t>S3IO通信異常調査</t>
+  </si>
+  <si>
+    <t>✓ 反映済み（LPF部分）</t>
+  </si>
+  <si>
+    <t>No6追加解析</t>
+  </si>
+  <si>
+    <t>ワーニング増加原因解消</t>
+  </si>
+  <si>
+    <t>9-修正1</t>
+  </si>
+  <si>
+    <t>CD134エラー修正</t>
+  </si>
+  <si>
+    <t>✓ 完全反映</t>
+  </si>
+  <si>
+    <t>9-修正2</t>
+  </si>
+  <si>
+    <t>MT420/MT529修正</t>
+  </si>
+  <si>
+    <t>9-修正3</t>
+  </si>
+  <si>
+    <t>CLKCOM_OUTタイミング修正</t>
+  </si>
+  <si>
+    <t>この2点を修正して再コンパイルすれば、FDC制約とLPFタイミング制約が全て有効化され、CLKCOM_OUTのタイミング違反解消が期待できます。修正しますか？</t>
+  </si>
+  <si>
+    <t>Updated todo list tracking modification history and synthesis report review tasks</t>
+  </si>
+  <si>
+    <t>Update Todos</t>
+  </si>
+  <si>
+    <t> Read modification history (修正履歴.xlsx) - items No.1-9</t>
+  </si>
+  <si>
+    <t> Read synthesis report (SP0557_SP0557.srr) for errors/warnings</t>
+  </si>
+  <si>
+    <t> Read place &amp; route / timing reports for MAP/PAR results</t>
+  </si>
+  <si>
+    <t> Verify RTL source files contain the expected changes from No.9 sheet</t>
+  </si>
+  <si>
+    <t> Verify pll_gen.fdc is being loaded by synthesis and check why MT420/MT529 remain</t>
+  </si>
+  <si>
+    <t> Compare previous vs current warning counts</t>
+  </si>
+  <si>
+    <t> Report verification results</t>
+  </si>
+  <si>
+    <t>これはdiamondツール上で実施する手順ではないのですか</t>
+  </si>
+  <si>
+    <t>はい、その通りです。</t>
+  </si>
+  <si>
+    <t>Diamond上での操作手順</t>
+  </si>
+  <si>
+    <t>3. 以下の2ファイルを追加:</t>
+  </si>
+  <si>
+    <t>5. 保存してから再合成（Synthesize）を実行</t>
+  </si>
+  <si>
+    <t>残りの問題: LPFクロックネット名の修正</t>
+  </si>
+  <si>
+    <t>修正前</t>
+  </si>
+  <si>
+    <t>修正後</t>
+  </si>
+  <si>
+    <t>"slv_com_top_inst.CLK2"</t>
+  </si>
+  <si>
+    <t>"slv_com_top_inst.CLKCOM_OUT"</t>
+  </si>
+  <si>
+    <t>"slv_com_top_inst.CLK2A"</t>
+  </si>
+  <si>
+    <t>"slv_com_top_inst/CLK2A"</t>
+  </si>
+  <si>
+    <t>&lt;Source name="RTL/IPcore/pll_gen/pll_gen.fdc" type="FDC" type_short="FDC"&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    &lt;Options/&gt;</t>
+  </si>
+  <si>
+    <t>&lt;/Source&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Source name="SP0557/SP0557.fdc" type="FDC" type_short="FDC"&gt;</t>
+  </si>
+  <si>
+    <t>pll_gen.fdc の内容は正しく修正されています:</t>
+  </si>
+  <si>
+    <t>{p:CLKOP} → {n:CLKOP_t} ✓</t>
+  </si>
+  <si>
+    <t>{p:CLKOS} → {n:CLKOS_t} ✓</t>
+  </si>
+  <si>
+    <t>{p:CLKOS2} → {n:CLKOS2_t} ✓</t>
+  </si>
+  <si>
+    <t>{p:CLKOS3} → {n:CLKOS3_t} ✓</t>
+  </si>
+  <si>
+    <t>全クロックが -clockgroup pll_clks で統一 ✓</t>
+  </si>
+  <si>
+    <t>stdout.log にFDCファイル削除の記録:</t>
+  </si>
+  <si>
+    <t>slv_com_top_inst/CLK2A (.ではなく/)</t>
+  </si>
+  <si>
+    <t>CLK1→CLKCOM_OUT: 59パスがFREQUENCY NET "slv_com_top_inst.CLKCOM_OUT" 100MHzで解析（MULTICYCLEなし）</t>
+  </si>
+  <si>
+    <t>CLKCOM_OUT→CLK1: 23パスがFREQUENCY NET "slv_com_top_inst.CLK1" 10MHzで解析（MULTICYCLEなし）</t>
+  </si>
+  <si>
+    <t>Hold違反: CLK1ドメインで -0.321ns（s_LRSTb_r44, TX_RSTb_i_r8）</t>
+  </si>
+  <si>
+    <t>SP0557.ldf に以下の2行を追加する必要があります:</t>
+  </si>
+  <si>
+    <t>こちらは .lpf ファイルのテキスト修正なので、Diamond上でもテキストエディタでもどちらでも対応可能です。修正箇所は以下の通りです:</t>
+  </si>
+  <si>
+    <r>
+      <t>0件</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> (合成成功)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1件</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> (CLKCOM_OUT: 98.483MHz &lt; 100MHz)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1件</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> (CLK1: -0.321ns)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CD134エラー </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>0件</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>根本原因</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: SP0557.ldf（Diamondプロジェクトファイル）に pll_gen.fdc と SP0557.fdc が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ソースとして登録されていない</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>。VHDLファイルとLPFファイルのみが登録されています。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>結果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: MT420/MT529ワーニングが</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>5件とも残存</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>適用済み</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> (LPF 66行目)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>適用済み</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> (LPF 362行目)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>これにより以下の制約が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>全て無視</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>されています:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>これが</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>CLKCOM_OUTタイミング違反の直接原因</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>です（98.483MHz &lt; 100MHz）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>一部のみ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> (ネット名不一致で制約無視)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>一部のみ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> (同上)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>✗ 未反映</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> (LDFにFDC未登録)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>✗ 未反映</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> (ネット名不一致)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>結論</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: RTLソースコードの修正は全て正しく適用されていますが、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>2つの設定上の問題</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>により、コンパイル結果には完全に反映されていません。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. FDCファイルがDiamondプロジェクトに未登録</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> → MT420/MT529残存</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. LPFのクロックネット名不一致</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> (CLK2 ≠ CLKCOM_OUT, .CLK2A ≠ /CLK2A) → MULTICYCLE/BLOCK PATH制約が無視されタイミング違反継続</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SP0557.ldf はDiamond GUIで管理されるプロジェクトファイルなので、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>FDCファイルの登録はDiamond上で行うのが正しい手順</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>です。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. Diamond</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>でプロジェクト SP0557.ldf を開く</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. File List</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> パネルで右クリック → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>Add</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>Existing File...</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4. ファイルタイプが </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>FDC (Synplify Forward Declaration Constraint)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> として認識されていることを確認</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>.ldf をテキストエディタで直接編集しても動作はしますが、Diamondが管理するXML構造なので、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>Diamond GUI上で追加する方が安全</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>です。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>LPF内の </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>Section 2, 4, 5, 6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> の計8箇所が対象です。こちらの修正は私の方で実施できますが、対応しますか？</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="30">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6450,6 +7431,21 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -6515,7 +7511,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6782,6 +7778,30 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7254,9 +8274,15 @@
       <c r="F13" s="26"/>
     </row>
     <row r="14" spans="3:6">
-      <c r="C14" s="26"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="27"/>
+      <c r="C14" s="26">
+        <v>10</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>836</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>837</v>
+      </c>
       <c r="F14" s="26"/>
     </row>
     <row r="15" spans="3:6">
@@ -7988,6 +9014,1533 @@
       <c r="A181" s="25" t="s">
         <v>783</v>
       </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80AF1D6C-FC01-45A2-8677-95498AA084BB}">
+  <dimension ref="A1:E149"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="77.75" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="5" max="5" width="7.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A1" s="89" t="s">
+        <v>839</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+    </row>
+    <row r="2" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A2" s="74" t="s">
+        <v>840</v>
+      </c>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+    </row>
+    <row r="3" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A3" s="72"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+    </row>
+    <row r="4" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A4" s="89" t="s">
+        <v>841</v>
+      </c>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+    </row>
+    <row r="5" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A5" s="91" t="s">
+        <v>842</v>
+      </c>
+      <c r="B5" s="92" t="s">
+        <v>557</v>
+      </c>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+    </row>
+    <row r="6" spans="1:5" s="90" customFormat="1" ht="20.25" thickBot="1">
+      <c r="A6" s="79" t="s">
+        <v>843</v>
+      </c>
+      <c r="B6" s="93" t="s">
+        <v>996</v>
+      </c>
+      <c r="C6" s="72"/>
+      <c r="D6" s="72"/>
+      <c r="E6" s="72"/>
+    </row>
+    <row r="7" spans="1:5" s="90" customFormat="1" ht="33.75" thickBot="1">
+      <c r="A7" s="79" t="s">
+        <v>844</v>
+      </c>
+      <c r="B7" s="93" t="s">
+        <v>997</v>
+      </c>
+      <c r="C7" s="72"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
+    </row>
+    <row r="8" spans="1:5" s="90" customFormat="1" ht="20.25" thickBot="1">
+      <c r="A8" s="79" t="s">
+        <v>845</v>
+      </c>
+      <c r="B8" s="93" t="s">
+        <v>998</v>
+      </c>
+      <c r="C8" s="72"/>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
+    </row>
+    <row r="9" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A9" s="79" t="s">
+        <v>846</v>
+      </c>
+      <c r="B9" s="89" t="s">
+        <v>847</v>
+      </c>
+      <c r="C9" s="72"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72"/>
+    </row>
+    <row r="10" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A10" s="72"/>
+      <c r="B10" s="72"/>
+      <c r="C10" s="72"/>
+      <c r="D10" s="72"/>
+      <c r="E10" s="72"/>
+    </row>
+    <row r="11" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A11" s="89" t="s">
+        <v>848</v>
+      </c>
+      <c r="B11" s="72"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="72"/>
+      <c r="E11" s="72"/>
+    </row>
+    <row r="12" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A12" s="89" t="s">
+        <v>849</v>
+      </c>
+      <c r="B12" s="72"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+    </row>
+    <row r="13" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A13" s="91" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="91" t="s">
+        <v>658</v>
+      </c>
+      <c r="C13" s="91" t="s">
+        <v>850</v>
+      </c>
+      <c r="D13" s="92" t="s">
+        <v>851</v>
+      </c>
+      <c r="E13" s="72"/>
+    </row>
+    <row r="14" spans="1:5" s="90" customFormat="1" ht="33.75" thickBot="1">
+      <c r="A14" s="79" t="s">
+        <v>852</v>
+      </c>
+      <c r="B14" s="79" t="s">
+        <v>853</v>
+      </c>
+      <c r="C14" s="94" t="s">
+        <v>854</v>
+      </c>
+      <c r="D14" s="81" t="s">
+        <v>999</v>
+      </c>
+      <c r="E14" s="72"/>
+    </row>
+    <row r="15" spans="1:5" s="90" customFormat="1" ht="33.75" thickBot="1">
+      <c r="A15" s="79" t="s">
+        <v>855</v>
+      </c>
+      <c r="B15" s="79" t="s">
+        <v>856</v>
+      </c>
+      <c r="C15" s="94" t="s">
+        <v>854</v>
+      </c>
+      <c r="D15" s="81" t="s">
+        <v>999</v>
+      </c>
+      <c r="E15" s="72"/>
+    </row>
+    <row r="16" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A16" s="79" t="s">
+        <v>857</v>
+      </c>
+      <c r="B16" s="79" t="s">
+        <v>858</v>
+      </c>
+      <c r="C16" s="94" t="s">
+        <v>854</v>
+      </c>
+      <c r="D16" s="74" t="s">
+        <v>999</v>
+      </c>
+      <c r="E16" s="72"/>
+    </row>
+    <row r="17" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A17" s="74" t="s">
+        <v>859</v>
+      </c>
+      <c r="B17" s="72"/>
+      <c r="C17" s="72"/>
+      <c r="D17" s="72"/>
+      <c r="E17" s="72"/>
+    </row>
+    <row r="18" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A18" s="72"/>
+      <c r="B18" s="72"/>
+      <c r="C18" s="72"/>
+      <c r="D18" s="72"/>
+      <c r="E18" s="72"/>
+    </row>
+    <row r="19" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A19" s="89" t="s">
+        <v>860</v>
+      </c>
+      <c r="B19" s="72"/>
+      <c r="C19" s="72"/>
+      <c r="D19" s="72"/>
+      <c r="E19" s="72"/>
+    </row>
+    <row r="20" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A20" s="74" t="s">
+        <v>983</v>
+      </c>
+      <c r="B20" s="72"/>
+      <c r="C20" s="72"/>
+      <c r="D20" s="72"/>
+      <c r="E20" s="72"/>
+    </row>
+    <row r="21" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A21" s="75"/>
+      <c r="B21" s="72"/>
+      <c r="C21" s="72"/>
+      <c r="D21" s="72"/>
+      <c r="E21" s="72"/>
+    </row>
+    <row r="22" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A22" s="75" t="s">
+        <v>984</v>
+      </c>
+      <c r="B22" s="72"/>
+      <c r="C22" s="72"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+    </row>
+    <row r="23" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A23" s="75" t="s">
+        <v>985</v>
+      </c>
+      <c r="B23" s="72"/>
+      <c r="C23" s="72"/>
+      <c r="D23" s="72"/>
+      <c r="E23" s="72"/>
+    </row>
+    <row r="24" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A24" s="75" t="s">
+        <v>986</v>
+      </c>
+      <c r="B24" s="72"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+    </row>
+    <row r="25" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A25" s="75" t="s">
+        <v>987</v>
+      </c>
+      <c r="B25" s="72"/>
+      <c r="C25" s="72"/>
+      <c r="D25" s="72"/>
+      <c r="E25" s="72"/>
+    </row>
+    <row r="26" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A26" s="75" t="s">
+        <v>988</v>
+      </c>
+      <c r="B26" s="72"/>
+      <c r="C26" s="72"/>
+      <c r="D26" s="72"/>
+      <c r="E26" s="72"/>
+    </row>
+    <row r="27" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A27" s="74"/>
+      <c r="B27" s="72"/>
+      <c r="C27" s="72"/>
+      <c r="D27" s="72"/>
+      <c r="E27" s="72"/>
+    </row>
+    <row r="28" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A28" s="89" t="s">
+        <v>861</v>
+      </c>
+      <c r="B28" s="72"/>
+      <c r="C28" s="72"/>
+      <c r="D28" s="72"/>
+      <c r="E28" s="72"/>
+    </row>
+    <row r="29" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A29" s="74" t="s">
+        <v>862</v>
+      </c>
+      <c r="B29" s="72"/>
+      <c r="C29" s="72"/>
+      <c r="D29" s="72"/>
+      <c r="E29" s="72"/>
+    </row>
+    <row r="30" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A30" s="72" t="s">
+        <v>863</v>
+      </c>
+      <c r="B30" s="72"/>
+      <c r="C30" s="72"/>
+      <c r="D30" s="72"/>
+      <c r="E30" s="72"/>
+    </row>
+    <row r="31" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A31" s="74" t="s">
+        <v>989</v>
+      </c>
+      <c r="B31" s="72"/>
+      <c r="C31" s="72"/>
+      <c r="D31" s="72"/>
+      <c r="E31" s="72"/>
+    </row>
+    <row r="32" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A32" s="72" t="s">
+        <v>864</v>
+      </c>
+      <c r="B32" s="72"/>
+      <c r="C32" s="72"/>
+      <c r="D32" s="72"/>
+      <c r="E32" s="72"/>
+    </row>
+    <row r="33" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A33" s="72" t="s">
+        <v>865</v>
+      </c>
+      <c r="B33" s="72"/>
+      <c r="C33" s="72"/>
+      <c r="D33" s="72"/>
+      <c r="E33" s="72"/>
+    </row>
+    <row r="34" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A34" s="89" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B34" s="72"/>
+      <c r="C34" s="72"/>
+      <c r="D34" s="72"/>
+      <c r="E34" s="72"/>
+    </row>
+    <row r="35" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A35" s="89" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B35" s="72"/>
+      <c r="C35" s="72"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="72"/>
+    </row>
+    <row r="36" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A36" s="72" t="s">
+        <v>866</v>
+      </c>
+      <c r="B36" s="72"/>
+      <c r="C36" s="72"/>
+      <c r="D36" s="72"/>
+      <c r="E36" s="72"/>
+    </row>
+    <row r="37" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A37" s="72" t="s">
+        <v>867</v>
+      </c>
+      <c r="B37" s="72"/>
+      <c r="C37" s="72"/>
+      <c r="D37" s="72"/>
+      <c r="E37" s="72"/>
+    </row>
+    <row r="38" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A38" s="72" t="s">
+        <v>868</v>
+      </c>
+      <c r="B38" s="72"/>
+      <c r="C38" s="72"/>
+      <c r="D38" s="72"/>
+      <c r="E38" s="72"/>
+    </row>
+    <row r="39" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A39" s="72" t="s">
+        <v>869</v>
+      </c>
+      <c r="B39" s="72"/>
+      <c r="C39" s="72"/>
+      <c r="D39" s="72"/>
+      <c r="E39" s="72"/>
+    </row>
+    <row r="40" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A40" s="72" t="s">
+        <v>870</v>
+      </c>
+      <c r="B40" s="72"/>
+      <c r="C40" s="72"/>
+      <c r="D40" s="72"/>
+      <c r="E40" s="72"/>
+    </row>
+    <row r="41" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A41" s="74" t="s">
+        <v>871</v>
+      </c>
+      <c r="B41" s="72"/>
+      <c r="C41" s="72"/>
+      <c r="D41" s="72"/>
+      <c r="E41" s="72"/>
+    </row>
+    <row r="42" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A42" s="72"/>
+      <c r="B42" s="72"/>
+      <c r="C42" s="72"/>
+      <c r="D42" s="72"/>
+      <c r="E42" s="72"/>
+    </row>
+    <row r="43" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A43" s="89" t="s">
+        <v>872</v>
+      </c>
+      <c r="B43" s="72"/>
+      <c r="C43" s="72"/>
+      <c r="D43" s="72"/>
+      <c r="E43" s="72"/>
+    </row>
+    <row r="44" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A44" s="91" t="s">
+        <v>70</v>
+      </c>
+      <c r="B44" s="92" t="s">
+        <v>71</v>
+      </c>
+      <c r="C44" s="72"/>
+      <c r="D44" s="72"/>
+      <c r="E44" s="72"/>
+    </row>
+    <row r="45" spans="1:5" s="90" customFormat="1" ht="20.25" thickBot="1">
+      <c r="A45" s="79" t="s">
+        <v>873</v>
+      </c>
+      <c r="B45" s="93" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C45" s="72"/>
+      <c r="D45" s="72"/>
+      <c r="E45" s="72"/>
+    </row>
+    <row r="46" spans="1:5" s="90" customFormat="1" ht="20.25" thickBot="1">
+      <c r="A46" s="79" t="s">
+        <v>874</v>
+      </c>
+      <c r="B46" s="93" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C46" s="72"/>
+      <c r="D46" s="72"/>
+      <c r="E46" s="72"/>
+    </row>
+    <row r="47" spans="1:5" s="90" customFormat="1" ht="20.25" thickBot="1">
+      <c r="A47" s="79" t="s">
+        <v>875</v>
+      </c>
+      <c r="B47" s="93" t="s">
+        <v>876</v>
+      </c>
+      <c r="C47" s="72"/>
+      <c r="D47" s="72"/>
+      <c r="E47" s="72"/>
+    </row>
+    <row r="48" spans="1:5" s="90" customFormat="1" ht="20.25" thickBot="1">
+      <c r="A48" s="79" t="s">
+        <v>877</v>
+      </c>
+      <c r="B48" s="93" t="s">
+        <v>876</v>
+      </c>
+      <c r="C48" s="72"/>
+      <c r="D48" s="72"/>
+      <c r="E48" s="72"/>
+    </row>
+    <row r="49" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A49" s="79" t="s">
+        <v>878</v>
+      </c>
+      <c r="B49" s="89" t="s">
+        <v>876</v>
+      </c>
+      <c r="C49" s="72"/>
+      <c r="D49" s="72"/>
+      <c r="E49" s="72"/>
+    </row>
+    <row r="50" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A50" s="89" t="s">
+        <v>879</v>
+      </c>
+      <c r="B50" s="72"/>
+      <c r="C50" s="72"/>
+      <c r="D50" s="72"/>
+      <c r="E50" s="72"/>
+    </row>
+    <row r="51" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A51" s="91" t="s">
+        <v>880</v>
+      </c>
+      <c r="B51" s="91" t="s">
+        <v>881</v>
+      </c>
+      <c r="C51" s="92" t="s">
+        <v>71</v>
+      </c>
+      <c r="D51" s="72"/>
+      <c r="E51" s="72"/>
+    </row>
+    <row r="52" spans="1:5" s="90" customFormat="1" ht="33.75" thickBot="1">
+      <c r="A52" s="79" t="s">
+        <v>882</v>
+      </c>
+      <c r="B52" s="79" t="s">
+        <v>883</v>
+      </c>
+      <c r="C52" s="93" t="s">
+        <v>884</v>
+      </c>
+      <c r="D52" s="72"/>
+      <c r="E52" s="72"/>
+    </row>
+    <row r="53" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A53" s="79" t="s">
+        <v>885</v>
+      </c>
+      <c r="B53" s="79" t="s">
+        <v>990</v>
+      </c>
+      <c r="C53" s="89" t="s">
+        <v>884</v>
+      </c>
+      <c r="D53" s="72"/>
+      <c r="E53" s="72"/>
+    </row>
+    <row r="54" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A54" s="74" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B54" s="72"/>
+      <c r="C54" s="72"/>
+      <c r="D54" s="72"/>
+      <c r="E54" s="72"/>
+    </row>
+    <row r="55" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A55" s="91" t="s">
+        <v>886</v>
+      </c>
+      <c r="B55" s="91" t="s">
+        <v>887</v>
+      </c>
+      <c r="C55" s="92" t="s">
+        <v>888</v>
+      </c>
+      <c r="D55" s="72"/>
+      <c r="E55" s="72"/>
+    </row>
+    <row r="56" spans="1:5" s="90" customFormat="1" ht="132.75" thickBot="1">
+      <c r="A56" s="79" t="s">
+        <v>889</v>
+      </c>
+      <c r="B56" s="79" t="s">
+        <v>890</v>
+      </c>
+      <c r="C56" s="81" t="s">
+        <v>891</v>
+      </c>
+      <c r="D56" s="72"/>
+      <c r="E56" s="72"/>
+    </row>
+    <row r="57" spans="1:5" s="90" customFormat="1" ht="83.25" thickBot="1">
+      <c r="A57" s="79" t="s">
+        <v>892</v>
+      </c>
+      <c r="B57" s="79" t="s">
+        <v>893</v>
+      </c>
+      <c r="C57" s="81" t="s">
+        <v>894</v>
+      </c>
+      <c r="D57" s="72"/>
+      <c r="E57" s="72"/>
+    </row>
+    <row r="58" spans="1:5" s="90" customFormat="1" ht="99.75" thickBot="1">
+      <c r="A58" s="94" t="s">
+        <v>895</v>
+      </c>
+      <c r="B58" s="94" t="s">
+        <v>896</v>
+      </c>
+      <c r="C58" s="93" t="s">
+        <v>897</v>
+      </c>
+      <c r="D58" s="72"/>
+      <c r="E58" s="72"/>
+    </row>
+    <row r="59" spans="1:5" s="90" customFormat="1" ht="66">
+      <c r="A59" s="79" t="s">
+        <v>898</v>
+      </c>
+      <c r="B59" s="79" t="s">
+        <v>899</v>
+      </c>
+      <c r="C59" s="74" t="s">
+        <v>900</v>
+      </c>
+      <c r="D59" s="72"/>
+      <c r="E59" s="72"/>
+    </row>
+    <row r="60" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A60" s="89" t="s">
+        <v>901</v>
+      </c>
+      <c r="B60" s="72"/>
+      <c r="C60" s="72"/>
+      <c r="D60" s="72"/>
+      <c r="E60" s="72"/>
+    </row>
+    <row r="61" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A61" s="74" t="s">
+        <v>991</v>
+      </c>
+      <c r="B61" s="72"/>
+      <c r="C61" s="72"/>
+      <c r="D61" s="72"/>
+      <c r="E61" s="72"/>
+    </row>
+    <row r="62" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A62" s="74" t="s">
+        <v>992</v>
+      </c>
+      <c r="B62" s="72"/>
+      <c r="C62" s="72"/>
+      <c r="D62" s="72"/>
+      <c r="E62" s="72"/>
+    </row>
+    <row r="63" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A63" s="74" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B63" s="72"/>
+      <c r="C63" s="72"/>
+      <c r="D63" s="72"/>
+      <c r="E63" s="72"/>
+    </row>
+    <row r="64" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A64" s="72"/>
+      <c r="B64" s="72"/>
+      <c r="C64" s="72"/>
+      <c r="D64" s="72"/>
+      <c r="E64" s="72"/>
+    </row>
+    <row r="65" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A65" s="89" t="s">
+        <v>902</v>
+      </c>
+      <c r="B65" s="72"/>
+      <c r="C65" s="72"/>
+      <c r="D65" s="72"/>
+      <c r="E65" s="72"/>
+    </row>
+    <row r="66" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A66" s="91" t="s">
+        <v>903</v>
+      </c>
+      <c r="B66" s="91" t="s">
+        <v>887</v>
+      </c>
+      <c r="C66" s="91" t="s">
+        <v>904</v>
+      </c>
+      <c r="D66" s="91" t="s">
+        <v>905</v>
+      </c>
+      <c r="E66" s="92" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" s="90" customFormat="1" ht="33.75" thickBot="1">
+      <c r="A67" s="79" t="s">
+        <v>95</v>
+      </c>
+      <c r="B67" s="79" t="s">
+        <v>906</v>
+      </c>
+      <c r="C67" s="79" t="s">
+        <v>907</v>
+      </c>
+      <c r="D67" s="94" t="s">
+        <v>908</v>
+      </c>
+      <c r="E67" s="93" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" s="90" customFormat="1" ht="33.75" thickBot="1">
+      <c r="A68" s="79" t="s">
+        <v>910</v>
+      </c>
+      <c r="B68" s="79" t="s">
+        <v>906</v>
+      </c>
+      <c r="C68" s="79" t="s">
+        <v>911</v>
+      </c>
+      <c r="D68" s="79" t="s">
+        <v>912</v>
+      </c>
+      <c r="E68" s="81" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" s="90" customFormat="1" ht="33.75" thickBot="1">
+      <c r="A69" s="79" t="s">
+        <v>101</v>
+      </c>
+      <c r="B69" s="79" t="s">
+        <v>914</v>
+      </c>
+      <c r="C69" s="79" t="s">
+        <v>915</v>
+      </c>
+      <c r="D69" s="79" t="s">
+        <v>916</v>
+      </c>
+      <c r="E69" s="81" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" s="90" customFormat="1" ht="33.75" thickBot="1">
+      <c r="A70" s="79" t="s">
+        <v>917</v>
+      </c>
+      <c r="B70" s="79" t="s">
+        <v>918</v>
+      </c>
+      <c r="C70" s="79" t="s">
+        <v>919</v>
+      </c>
+      <c r="D70" s="79" t="s">
+        <v>916</v>
+      </c>
+      <c r="E70" s="81" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A71" s="79" t="s">
+        <v>920</v>
+      </c>
+      <c r="B71" s="79" t="s">
+        <v>510</v>
+      </c>
+      <c r="C71" s="79" t="s">
+        <v>510</v>
+      </c>
+      <c r="D71" s="79" t="s">
+        <v>510</v>
+      </c>
+      <c r="E71" s="74" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A72" s="74" t="s">
+        <v>993</v>
+      </c>
+      <c r="B72" s="72"/>
+      <c r="C72" s="72"/>
+      <c r="D72" s="72"/>
+      <c r="E72" s="72"/>
+    </row>
+    <row r="73" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A73" s="72"/>
+      <c r="B73" s="72"/>
+      <c r="C73" s="72"/>
+      <c r="D73" s="72"/>
+      <c r="E73" s="72"/>
+    </row>
+    <row r="74" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A74" s="89" t="s">
+        <v>922</v>
+      </c>
+      <c r="B74" s="72"/>
+      <c r="C74" s="72"/>
+      <c r="D74" s="72"/>
+      <c r="E74" s="72"/>
+    </row>
+    <row r="75" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A75" s="89" t="s">
+        <v>923</v>
+      </c>
+      <c r="B75" s="72"/>
+      <c r="C75" s="72"/>
+      <c r="D75" s="72"/>
+      <c r="E75" s="72"/>
+    </row>
+    <row r="76" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A76" s="74" t="s">
+        <v>994</v>
+      </c>
+      <c r="B76" s="72"/>
+      <c r="C76" s="72"/>
+      <c r="D76" s="72"/>
+      <c r="E76" s="72"/>
+    </row>
+    <row r="77" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A77" s="72" t="s">
+        <v>979</v>
+      </c>
+      <c r="B77" s="72"/>
+      <c r="C77" s="72"/>
+      <c r="D77" s="72"/>
+      <c r="E77" s="72"/>
+    </row>
+    <row r="78" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A78" s="72" t="s">
+        <v>980</v>
+      </c>
+      <c r="B78" s="72"/>
+      <c r="C78" s="72"/>
+      <c r="D78" s="72"/>
+      <c r="E78" s="72"/>
+    </row>
+    <row r="79" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A79" s="72" t="s">
+        <v>981</v>
+      </c>
+      <c r="B79" s="72"/>
+      <c r="C79" s="72"/>
+      <c r="D79" s="72"/>
+      <c r="E79" s="72"/>
+    </row>
+    <row r="80" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A80" s="72" t="s">
+        <v>982</v>
+      </c>
+      <c r="B80" s="72"/>
+      <c r="C80" s="72"/>
+      <c r="D80" s="72"/>
+      <c r="E80" s="72"/>
+    </row>
+    <row r="81" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A81" s="72" t="s">
+        <v>980</v>
+      </c>
+      <c r="B81" s="72"/>
+      <c r="C81" s="72"/>
+      <c r="D81" s="72"/>
+      <c r="E81" s="72"/>
+    </row>
+    <row r="82" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A82" s="72" t="s">
+        <v>981</v>
+      </c>
+      <c r="B82" s="72"/>
+      <c r="C82" s="72"/>
+      <c r="D82" s="72"/>
+      <c r="E82" s="72"/>
+    </row>
+    <row r="83" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A83" s="74" t="s">
+        <v>924</v>
+      </c>
+      <c r="B83" s="72"/>
+      <c r="C83" s="72"/>
+      <c r="D83" s="72"/>
+      <c r="E83" s="72"/>
+    </row>
+    <row r="84" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A84" s="75"/>
+      <c r="B84" s="72"/>
+      <c r="C84" s="72"/>
+      <c r="D84" s="72"/>
+      <c r="E84" s="72"/>
+    </row>
+    <row r="85" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A85" s="75" t="s">
+        <v>925</v>
+      </c>
+      <c r="B85" s="72"/>
+      <c r="C85" s="72"/>
+      <c r="D85" s="72"/>
+      <c r="E85" s="72"/>
+    </row>
+    <row r="86" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A86" s="75" t="s">
+        <v>926</v>
+      </c>
+      <c r="B86" s="72"/>
+      <c r="C86" s="72"/>
+      <c r="D86" s="72"/>
+      <c r="E86" s="72"/>
+    </row>
+    <row r="87" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A87" s="75" t="s">
+        <v>927</v>
+      </c>
+      <c r="B87" s="72"/>
+      <c r="C87" s="72"/>
+      <c r="D87" s="72"/>
+      <c r="E87" s="72"/>
+    </row>
+    <row r="88" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A88" s="74"/>
+      <c r="B88" s="72"/>
+      <c r="C88" s="72"/>
+      <c r="D88" s="72"/>
+      <c r="E88" s="72"/>
+    </row>
+    <row r="89" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A89" s="89" t="s">
+        <v>928</v>
+      </c>
+      <c r="B89" s="72"/>
+      <c r="C89" s="72"/>
+      <c r="D89" s="72"/>
+      <c r="E89" s="72"/>
+    </row>
+    <row r="90" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A90" s="72" t="s">
+        <v>929</v>
+      </c>
+      <c r="B90" s="72"/>
+      <c r="C90" s="72"/>
+      <c r="D90" s="72"/>
+      <c r="E90" s="72"/>
+    </row>
+    <row r="91" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A91" s="72" t="s">
+        <v>930</v>
+      </c>
+      <c r="B91" s="72"/>
+      <c r="C91" s="72"/>
+      <c r="D91" s="72"/>
+      <c r="E91" s="72"/>
+    </row>
+    <row r="92" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A92" s="72" t="s">
+        <v>931</v>
+      </c>
+      <c r="B92" s="72"/>
+      <c r="C92" s="72"/>
+      <c r="D92" s="72"/>
+      <c r="E92" s="72"/>
+    </row>
+    <row r="93" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A93" s="74" t="s">
+        <v>932</v>
+      </c>
+      <c r="B93" s="72"/>
+      <c r="C93" s="72"/>
+      <c r="D93" s="72"/>
+      <c r="E93" s="72"/>
+    </row>
+    <row r="94" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A94" s="74" t="s">
+        <v>924</v>
+      </c>
+      <c r="B94" s="72"/>
+      <c r="C94" s="72"/>
+      <c r="D94" s="72"/>
+      <c r="E94" s="72"/>
+    </row>
+    <row r="95" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A95" s="75"/>
+      <c r="B95" s="72"/>
+      <c r="C95" s="72"/>
+      <c r="D95" s="72"/>
+      <c r="E95" s="72"/>
+    </row>
+    <row r="96" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A96" s="75" t="s">
+        <v>933</v>
+      </c>
+      <c r="B96" s="72"/>
+      <c r="C96" s="72"/>
+      <c r="D96" s="72"/>
+      <c r="E96" s="72"/>
+    </row>
+    <row r="97" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A97" s="75" t="s">
+        <v>934</v>
+      </c>
+      <c r="B97" s="72"/>
+      <c r="C97" s="72"/>
+      <c r="D97" s="72"/>
+      <c r="E97" s="72"/>
+    </row>
+    <row r="98" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A98" s="74"/>
+      <c r="B98" s="72"/>
+      <c r="C98" s="72"/>
+      <c r="D98" s="72"/>
+      <c r="E98" s="72"/>
+    </row>
+    <row r="99" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A99" s="72"/>
+      <c r="B99" s="72"/>
+      <c r="C99" s="72"/>
+      <c r="D99" s="72"/>
+      <c r="E99" s="72"/>
+    </row>
+    <row r="100" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A100" s="89" t="s">
+        <v>935</v>
+      </c>
+      <c r="B100" s="72"/>
+      <c r="C100" s="72"/>
+      <c r="D100" s="72"/>
+      <c r="E100" s="72"/>
+    </row>
+    <row r="101" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A101" s="91" t="s">
+        <v>936</v>
+      </c>
+      <c r="B101" s="91" t="s">
+        <v>658</v>
+      </c>
+      <c r="C101" s="91" t="s">
+        <v>937</v>
+      </c>
+      <c r="D101" s="92" t="s">
+        <v>851</v>
+      </c>
+      <c r="E101" s="72"/>
+    </row>
+    <row r="102" spans="1:5" s="90" customFormat="1" ht="83.25" thickBot="1">
+      <c r="A102" s="79">
+        <v>1</v>
+      </c>
+      <c r="B102" s="79" t="s">
+        <v>938</v>
+      </c>
+      <c r="C102" s="79" t="s">
+        <v>939</v>
+      </c>
+      <c r="D102" s="93" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E102" s="72"/>
+    </row>
+    <row r="103" spans="1:5" s="90" customFormat="1" ht="33.75" thickBot="1">
+      <c r="A103" s="79">
+        <v>2</v>
+      </c>
+      <c r="B103" s="79" t="s">
+        <v>940</v>
+      </c>
+      <c r="C103" s="79" t="s">
+        <v>939</v>
+      </c>
+      <c r="D103" s="93" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E103" s="72"/>
+    </row>
+    <row r="104" spans="1:5" s="90" customFormat="1" ht="33.75" thickBot="1">
+      <c r="A104" s="79">
+        <v>3</v>
+      </c>
+      <c r="B104" s="79" t="s">
+        <v>941</v>
+      </c>
+      <c r="C104" s="79" t="s">
+        <v>939</v>
+      </c>
+      <c r="D104" s="81" t="s">
+        <v>942</v>
+      </c>
+      <c r="E104" s="72"/>
+    </row>
+    <row r="105" spans="1:5" s="90" customFormat="1" ht="20.25" thickBot="1">
+      <c r="A105" s="79">
+        <v>4</v>
+      </c>
+      <c r="B105" s="79" t="s">
+        <v>943</v>
+      </c>
+      <c r="C105" s="79" t="s">
+        <v>510</v>
+      </c>
+      <c r="D105" s="81" t="s">
+        <v>510</v>
+      </c>
+      <c r="E105" s="72"/>
+    </row>
+    <row r="106" spans="1:5" s="90" customFormat="1" ht="66.75" thickBot="1">
+      <c r="A106" s="79">
+        <v>5</v>
+      </c>
+      <c r="B106" s="79" t="s">
+        <v>944</v>
+      </c>
+      <c r="C106" s="79" t="s">
+        <v>939</v>
+      </c>
+      <c r="D106" s="93" t="s">
+        <v>945</v>
+      </c>
+      <c r="E106" s="72"/>
+    </row>
+    <row r="107" spans="1:5" s="90" customFormat="1" ht="66.75" thickBot="1">
+      <c r="A107" s="79">
+        <v>6</v>
+      </c>
+      <c r="B107" s="79" t="s">
+        <v>946</v>
+      </c>
+      <c r="C107" s="79" t="s">
+        <v>939</v>
+      </c>
+      <c r="D107" s="81" t="s">
+        <v>947</v>
+      </c>
+      <c r="E107" s="72"/>
+    </row>
+    <row r="108" spans="1:5" s="90" customFormat="1" ht="33.75" thickBot="1">
+      <c r="A108" s="79">
+        <v>7</v>
+      </c>
+      <c r="B108" s="79" t="s">
+        <v>948</v>
+      </c>
+      <c r="C108" s="79" t="s">
+        <v>939</v>
+      </c>
+      <c r="D108" s="81" t="s">
+        <v>942</v>
+      </c>
+      <c r="E108" s="72"/>
+    </row>
+    <row r="109" spans="1:5" s="90" customFormat="1" ht="33.75" thickBot="1">
+      <c r="A109" s="79">
+        <v>8</v>
+      </c>
+      <c r="B109" s="79" t="s">
+        <v>949</v>
+      </c>
+      <c r="C109" s="79" t="s">
+        <v>939</v>
+      </c>
+      <c r="D109" s="81" t="s">
+        <v>942</v>
+      </c>
+      <c r="E109" s="72"/>
+    </row>
+    <row r="110" spans="1:5" s="90" customFormat="1" ht="33.75" thickBot="1">
+      <c r="A110" s="79" t="s">
+        <v>950</v>
+      </c>
+      <c r="B110" s="79" t="s">
+        <v>951</v>
+      </c>
+      <c r="C110" s="79" t="s">
+        <v>939</v>
+      </c>
+      <c r="D110" s="93" t="s">
+        <v>952</v>
+      </c>
+      <c r="E110" s="72"/>
+    </row>
+    <row r="111" spans="1:5" s="90" customFormat="1" ht="66.75" thickBot="1">
+      <c r="A111" s="79" t="s">
+        <v>953</v>
+      </c>
+      <c r="B111" s="79" t="s">
+        <v>954</v>
+      </c>
+      <c r="C111" s="79" t="s">
+        <v>939</v>
+      </c>
+      <c r="D111" s="93" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E111" s="72"/>
+    </row>
+    <row r="112" spans="1:5" s="90" customFormat="1" ht="66">
+      <c r="A112" s="79" t="s">
+        <v>955</v>
+      </c>
+      <c r="B112" s="79" t="s">
+        <v>956</v>
+      </c>
+      <c r="C112" s="79" t="s">
+        <v>939</v>
+      </c>
+      <c r="D112" s="89" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E112" s="72"/>
+    </row>
+    <row r="113" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A113" s="89" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B113" s="72"/>
+      <c r="C113" s="72"/>
+      <c r="D113" s="72"/>
+      <c r="E113" s="72"/>
+    </row>
+    <row r="114" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A114" s="75"/>
+      <c r="B114" s="72"/>
+      <c r="C114" s="72"/>
+      <c r="D114" s="72"/>
+      <c r="E114" s="72"/>
+    </row>
+    <row r="115" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A115" s="95" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B115" s="72"/>
+      <c r="C115" s="72"/>
+      <c r="D115" s="72"/>
+      <c r="E115" s="72"/>
+    </row>
+    <row r="116" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A116" s="95" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B116" s="72"/>
+      <c r="C116" s="72"/>
+      <c r="D116" s="72"/>
+      <c r="E116" s="72"/>
+    </row>
+    <row r="117" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A117" s="74"/>
+      <c r="B117" s="72"/>
+      <c r="C117" s="72"/>
+      <c r="D117" s="72"/>
+      <c r="E117" s="72"/>
+    </row>
+    <row r="118" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A118" s="74" t="s">
+        <v>957</v>
+      </c>
+      <c r="B118" s="72"/>
+      <c r="C118" s="72"/>
+      <c r="D118" s="72"/>
+      <c r="E118" s="72"/>
+    </row>
+    <row r="119" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A119" s="74" t="s">
+        <v>958</v>
+      </c>
+      <c r="B119" s="72"/>
+      <c r="C119" s="72"/>
+      <c r="D119" s="72"/>
+      <c r="E119" s="72"/>
+    </row>
+    <row r="120" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A120" s="74" t="s">
+        <v>958</v>
+      </c>
+      <c r="B120" s="72"/>
+      <c r="C120" s="72"/>
+      <c r="D120" s="72"/>
+      <c r="E120" s="72"/>
+    </row>
+    <row r="121" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A121" s="74" t="s">
+        <v>959</v>
+      </c>
+      <c r="B121" s="72"/>
+      <c r="C121" s="72"/>
+      <c r="D121" s="72"/>
+      <c r="E121" s="72"/>
+    </row>
+    <row r="122" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A122" s="74" t="s">
+        <v>960</v>
+      </c>
+      <c r="B122" s="72"/>
+      <c r="C122" s="72"/>
+      <c r="D122" s="72"/>
+      <c r="E122" s="72"/>
+    </row>
+    <row r="123" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A123" s="74" t="s">
+        <v>961</v>
+      </c>
+      <c r="B123" s="72"/>
+      <c r="C123" s="72"/>
+      <c r="D123" s="72"/>
+      <c r="E123" s="72"/>
+    </row>
+    <row r="124" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A124" s="74" t="s">
+        <v>962</v>
+      </c>
+      <c r="B124" s="72"/>
+      <c r="C124" s="72"/>
+      <c r="D124" s="72"/>
+      <c r="E124" s="72"/>
+    </row>
+    <row r="125" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A125" s="74" t="s">
+        <v>963</v>
+      </c>
+      <c r="B125" s="72"/>
+      <c r="C125" s="72"/>
+      <c r="D125" s="72"/>
+      <c r="E125" s="72"/>
+    </row>
+    <row r="126" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A126" s="74" t="s">
+        <v>964</v>
+      </c>
+      <c r="B126" s="72"/>
+      <c r="C126" s="72"/>
+      <c r="D126" s="72"/>
+      <c r="E126" s="72"/>
+    </row>
+    <row r="127" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A127" s="74" t="s">
+        <v>965</v>
+      </c>
+      <c r="B127" s="72"/>
+      <c r="C127" s="72"/>
+      <c r="D127" s="72"/>
+      <c r="E127" s="72"/>
+    </row>
+    <row r="128" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A128" s="74" t="s">
+        <v>966</v>
+      </c>
+      <c r="B128" s="72"/>
+      <c r="C128" s="72"/>
+      <c r="D128" s="72"/>
+      <c r="E128" s="72"/>
+    </row>
+    <row r="129" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A129" s="74" t="s">
+        <v>838</v>
+      </c>
+      <c r="B129" s="72"/>
+      <c r="C129" s="72"/>
+      <c r="D129" s="72"/>
+      <c r="E129" s="72"/>
+    </row>
+    <row r="130" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A130" s="74" t="s">
+        <v>967</v>
+      </c>
+      <c r="B130" s="72"/>
+      <c r="C130" s="72"/>
+      <c r="D130" s="72"/>
+      <c r="E130" s="72"/>
+    </row>
+    <row r="131" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A131" s="74" t="s">
+        <v>968</v>
+      </c>
+      <c r="B131" s="72"/>
+      <c r="C131" s="72"/>
+      <c r="D131" s="72"/>
+      <c r="E131" s="72"/>
+    </row>
+    <row r="132" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A132" s="74" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B132" s="72"/>
+      <c r="C132" s="72"/>
+      <c r="D132" s="72"/>
+      <c r="E132" s="72"/>
+    </row>
+    <row r="133" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A133" s="89" t="s">
+        <v>969</v>
+      </c>
+      <c r="B133" s="72"/>
+      <c r="C133" s="72"/>
+      <c r="D133" s="72"/>
+      <c r="E133" s="72"/>
+    </row>
+    <row r="134" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A134" s="75"/>
+      <c r="B134" s="72"/>
+      <c r="C134" s="72"/>
+      <c r="D134" s="72"/>
+      <c r="E134" s="72"/>
+    </row>
+    <row r="135" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A135" s="95" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B135" s="72"/>
+      <c r="C135" s="72"/>
+      <c r="D135" s="72"/>
+      <c r="E135" s="72"/>
+    </row>
+    <row r="136" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A136" s="95" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B136" s="72"/>
+      <c r="C136" s="72"/>
+      <c r="D136" s="72"/>
+      <c r="E136" s="72"/>
+    </row>
+    <row r="137" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A137" s="75" t="s">
+        <v>970</v>
+      </c>
+      <c r="B137" s="72"/>
+      <c r="C137" s="72"/>
+      <c r="D137" s="72"/>
+      <c r="E137" s="72"/>
+    </row>
+    <row r="138" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A138" s="96" t="s">
+        <v>778</v>
+      </c>
+      <c r="B138" s="72"/>
+      <c r="C138" s="72"/>
+      <c r="D138" s="72"/>
+      <c r="E138" s="72"/>
+    </row>
+    <row r="139" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A139" s="96" t="s">
+        <v>625</v>
+      </c>
+      <c r="B139" s="72"/>
+      <c r="C139" s="72"/>
+      <c r="D139" s="72"/>
+      <c r="E139" s="72"/>
+    </row>
+    <row r="140" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A140" s="75" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B140" s="72"/>
+      <c r="C140" s="72"/>
+      <c r="D140" s="72"/>
+      <c r="E140" s="72"/>
+    </row>
+    <row r="141" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A141" s="75" t="s">
+        <v>971</v>
+      </c>
+      <c r="B141" s="72"/>
+      <c r="C141" s="72"/>
+      <c r="D141" s="72"/>
+      <c r="E141" s="72"/>
+    </row>
+    <row r="142" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A142" s="74"/>
+      <c r="B142" s="72"/>
+      <c r="C142" s="72"/>
+      <c r="D142" s="72"/>
+      <c r="E142" s="72"/>
+    </row>
+    <row r="143" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A143" s="74" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B143" s="72"/>
+      <c r="C143" s="72"/>
+      <c r="D143" s="72"/>
+      <c r="E143" s="72"/>
+    </row>
+    <row r="144" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A144" s="89" t="s">
+        <v>972</v>
+      </c>
+      <c r="B144" s="72"/>
+      <c r="C144" s="72"/>
+      <c r="D144" s="72"/>
+      <c r="E144" s="72"/>
+    </row>
+    <row r="145" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A145" s="74" t="s">
+        <v>995</v>
+      </c>
+      <c r="B145" s="72"/>
+      <c r="C145" s="72"/>
+      <c r="D145" s="72"/>
+      <c r="E145" s="72"/>
+    </row>
+    <row r="146" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A146" s="91" t="s">
+        <v>973</v>
+      </c>
+      <c r="B146" s="92" t="s">
+        <v>974</v>
+      </c>
+      <c r="C146" s="72"/>
+      <c r="D146" s="72"/>
+      <c r="E146" s="72"/>
+    </row>
+    <row r="147" spans="1:5" s="90" customFormat="1" ht="33.75" thickBot="1">
+      <c r="A147" s="79" t="s">
+        <v>975</v>
+      </c>
+      <c r="B147" s="81" t="s">
+        <v>976</v>
+      </c>
+      <c r="C147" s="72"/>
+      <c r="D147" s="72"/>
+      <c r="E147" s="72"/>
+    </row>
+    <row r="148" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A148" s="79" t="s">
+        <v>977</v>
+      </c>
+      <c r="B148" s="74" t="s">
+        <v>978</v>
+      </c>
+      <c r="C148" s="72"/>
+      <c r="D148" s="72"/>
+      <c r="E148" s="72"/>
+    </row>
+    <row r="149" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A149" s="74" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B149" s="72"/>
+      <c r="C149" s="72"/>
+      <c r="D149" s="72"/>
+      <c r="E149" s="72"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/PCBNo.10081/FPGA/修正履歴.xlsx
+++ b/PCBNo.10081/FPGA/修正履歴.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/512e22ffcc52695f/ドキュメント/GitHub/PCBNo.10081/PCBNo.10081/FPGA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FPGA work\PCBNo.10081\FPGA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{BCDA7BAB-8026-4C53-BAA1-6CFCABC79B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74324252-AD45-4920-A6B2-E6EB76FC6AC7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F38BC98-97EE-4E89-B636-CBEA2B7A2410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28320" firstSheet="2" activeTab="8" xr2:uid="{3A2BB469-6CC5-41C3-8C98-63503D4CF60C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{3A2BB469-6CC5-41C3-8C98-63503D4CF60C}"/>
   </bookViews>
   <sheets>
     <sheet name="修正履歴" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,9 @@
     <sheet name="No6" sheetId="8" r:id="rId7"/>
     <sheet name="No.7" sheetId="9" r:id="rId8"/>
     <sheet name="No.8" sheetId="10" r:id="rId9"/>
+    <sheet name="No.9" sheetId="11" r:id="rId10"/>
+    <sheet name="No.10" sheetId="12" r:id="rId11"/>
+    <sheet name="No.11" sheetId="13" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="1021">
   <si>
     <t>No</t>
     <phoneticPr fontId="1"/>
@@ -5579,12 +5582,1654 @@
       <t>: このブランチをmasterにマージ → Diamond でClean → Synthesize Design → 16件に戻るはず。</t>
     </r>
   </si>
+  <si>
+    <t>09_1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>No1~8が適応できているかの確認</t>
+    <rPh sb="6" eb="8">
+      <t>テキオウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>修正履歴No.1〜No.8の適用確認を行った結果、コードレベルでは全修正が適用済みだが、コンパイル結果に以下4つの残存問題がある。本計画でこれら全てを修正する。</t>
+  </si>
+  <si>
+    <t>修正1: CD134 識別子エラー修正（3件）</t>
+  </si>
+  <si>
+    <t>原因</t>
+  </si>
+  <si>
+    <t>変更前:</t>
+  </si>
+  <si>
+    <t>変更後:</t>
+  </si>
+  <si>
+    <t>-- ENB_START preservation handled by SP0557.fdc (Section 7N)</t>
+  </si>
+  <si>
+    <t>-- DATAOUT preservation handled by SP0557.fdc (Section 7E)</t>
+  </si>
+  <si>
+    <t>-- NODE preservation handled by SP0557.fdc (Section 7D)</t>
+  </si>
+  <si>
+    <t>### 原因</t>
+  </si>
+  <si>
+    <t>### 修正内容</t>
+  </si>
+  <si>
+    <t>修正4: SLICE使用率改善</t>
+  </si>
+  <si>
+    <t>対応方針</t>
+  </si>
+  <si>
+    <t>修正3の115MHz→100MHz変更により、以下の改善が期待される:</t>
+  </si>
+  <si>
+    <t>Synplifyのレジスタ複製削減（タイミング圧力緩和）</t>
+  </si>
+  <si>
+    <t>P&amp;Rの配置最適化余地拡大</t>
+  </si>
+  <si>
+    <t>推定効果: 89% → 85-87%程度</t>
+  </si>
+  <si>
+    <t>追加のRTL変更は行わない（修正2のFDCクロック定義が正しく適用されれば、合成最適化の質も改善される）。</t>
+  </si>
+  <si>
+    <t>修正対象ファイル一覧</t>
+  </si>
+  <si>
+    <t>RTL/SP0557/compactppmc/ppmc_ctrl.vhd</t>
+  </si>
+  <si>
+    <t>ENB_START属性削除</t>
+  </si>
+  <si>
+    <t>RTL/SP0557/slv_com/rx_com/dec6b_5b.vhd</t>
+  </si>
+  <si>
+    <t>DATAOUT属性削除</t>
+  </si>
+  <si>
+    <t>RTL/SP0557/slv_com/slv_ctrl/slv_rx_ctrl.vhd</t>
+  </si>
+  <si>
+    <t>NODE属性削除</t>
+  </si>
+  <si>
+    <t>RTL/IPcore/pll_gen/pll_gen.fdc</t>
+  </si>
+  <si>
+    <t>FPGA/SP0557.lpf</t>
+  </si>
+  <si>
+    <t>115MHz → 100MHz</t>
+  </si>
+  <si>
+    <t>修正適用後、Lattice Diamond / Synplifyでフルビルドを実施し、以下を確認:</t>
+  </si>
+  <si>
+    <t>BN137, MO160, MO129, CL177, CL240, CD638 が消滅したままであること</t>
+  </si>
+  <si>
+    <t>全クロックドメインの制約がPASSすること（CLKCOM_OUT含む）</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">RTLソースファイル内で </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>attribute syn_preserve of XXXX : signal is true;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> と記述しているが、対象がエンティティの</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>出力ポート</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>であるため、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: signal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> ではなく </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: port</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> を使う必要がある。FDCファイル(SP0557.fdc)には既に正しい制約が定義されているため、RTL内の重複属性を削除するのが最もクリーン。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ファイル1: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>PCBNo.10081/FPGA/RTL/SP0557/compactppmc/ppmc_ctrl.vhd</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> (133-136行)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">削除: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ENB_START</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> のsyn_preserve属性宣言（ENB_STARTは出力ポート）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>s_pls_ld</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> は内部signal なので残す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SP0557.fdc 7N節（246行: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>define_attribute {v:work.ppmc_ctrl} syn_preserve {1}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>）がモジュール全体を保護しているため、RTL属性は不要</t>
+    </r>
+  </si>
+  <si>
+    <t>attribute syn_preserve : boolean;</t>
+  </si>
+  <si>
+    <t>attribute syn_preserve of s_pls_ld  : signal is true;</t>
+  </si>
+  <si>
+    <t>attribute syn_preserve of ENB_START : signal is true;</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ファイル2: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>PCBNo.10081/FPGA/RTL/SP0557/slv_com/rx_com/dec6b_5b.vhd</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> (36-38行)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">削除: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>DATAOUT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> のsyn_preserve属性宣言（DATAOUTは出力ポート）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SP0557.fdc 7E節（166-171行）が合成後レジスタ名 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>DATAOUT_33_0_areg[*]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> で保護済み</t>
+    </r>
+  </si>
+  <si>
+    <t>attribute syn_preserve of DATAOUT : signal is true;</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ファイル3: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>PCBNo.10081/FPGA/RTL/SP0557/slv_com/slv_ctrl/slv_rx_ctrl.vhd</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> (90-94行)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">削除: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>NODE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> のsyn_preserve属性宣言（NODEは出力ポート）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>byte_cnt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> はinternal signal なので残す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SP0557.fdc 7D節（159-162行）が </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>NODE[0:3]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> を階層パス付きで保護済み</t>
+    </r>
+  </si>
+  <si>
+    <t>attribute syn_keep : boolean;</t>
+  </si>
+  <si>
+    <t>attribute syn_keep of byte_cnt : signal is true;</t>
+  </si>
+  <si>
+    <t>attribute syn_preserve of NODE : signal is true;</t>
+  </si>
+  <si>
+    <t>## 修正2: MT420/MT529 警告修正（10件）</t>
+  </si>
+  <si>
+    <t>`pll_gen.fdc` で `{p:CLKOP}` 等のポート参照構文を使用しているが、Synplifyは内部信号 `CLKOP_t` からクロックを推論し、`pll_gen|CLKOP_inferred_clock` という名前を生成する。FDCのポート参照と推論クロック名が一致しないため、FDCのdefine_clockが**黙殺**されている。</t>
+  </si>
+  <si>
+    <t>結果として全PLLクロックが `set_option -frequency 100.0` の10ns周期（100MHz）で処理され、実際の周波数と一致しないクロック（CLKOS2=20MHz, CLKOS3=10MHz）で不正確な合成最適化が行われている。</t>
+  </si>
+  <si>
+    <t>**ファイル: `PCBNo.10081/FPGA/RTL/IPcore/pll_gen/pll_gen.fdc`**</t>
+  </si>
+  <si>
+    <t>`{p:PORT}` 構文を `{n:SIGNAL}` 構文に変更し、Synplifyが実際に推論する内部信号名を参照する。</t>
+  </si>
+  <si>
+    <t>define_clock -name {CLKOP_100M} {p:CLKOP} -freq 100.000 ...</t>
+  </si>
+  <si>
+    <t>define_clock -name {CLKOS_100M_90} {p:CLKOS} -freq 100.000 ...</t>
+  </si>
+  <si>
+    <t>define_clock -name {CLKOS2_20M} {p:CLKOS2} -freq 20.000 ...</t>
+  </si>
+  <si>
+    <t>define_clock -name {CLKOS3_10M} {p:CLKOS3} -freq 10.000 ...</t>
+  </si>
+  <si>
+    <t>define_clock -name {CLKOP_100M} {n:CLKOP_t} -freq 100.000 ...</t>
+  </si>
+  <si>
+    <t>define_clock -name {CLKOS_100M_90} {n:CLKOS_t} -freq 100.000 ...</t>
+  </si>
+  <si>
+    <t>define_clock -name {CLKOS2_20M} {n:CLKOS2_t} -freq 20.000 ...</t>
+  </si>
+  <si>
+    <t>define_clock -name {CLKOS3_10M} {n:CLKOS3_t} -freq 10.000 ...</t>
+  </si>
+  <si>
+    <t>`CLKOP_t`, `CLKOS_t`, `CLKOS2_t`, `CLKOS3_t` は `pll_gen.vhd` の23-30行で宣言された内部信号で、EHXPLLLプリミティブの出力に直接接続されている（79-80行）。</t>
+  </si>
+  <si>
+    <t>**注意**: `{n:SIGNAL}` が効かない場合のフォールバックとして、EHXPLLLインスタンスの出力ピンを直接参照する構文も検討:</t>
+  </si>
+  <si>
+    <t>define_clock -name {CLKOP_100M} {n:PLLInst_0.CLKOP} -freq 100.000 ...</t>
+  </si>
+  <si>
+    <t>## 修正3: CLKCOM_OUT タイミング違反修正</t>
+  </si>
+  <si>
+    <t>LPFで100MHzクロックに115MHzのガードバンド制約を設定しているが、DCFIFO Block RAM出力→TX制御レジスタのクリティカルパスが9.823ns（C2Q: 5.830ns + routing: 2.874ns + LUT: 0.236ns）で、8.696ns（115MHz）の制約を1.275ns超過している。</t>
+  </si>
+  <si>
+    <t>100MHz（10ns周期）なら9.852nsの余裕があり、マージナルだがPASSする。</t>
+  </si>
+  <si>
+    <t>**ファイル: `PCBNo.10081/FPGA/SP0557.lpf` (303-304行)**</t>
+  </si>
+  <si>
+    <t>FREQUENCY NET "slv_com_top_inst.CLK2" 115.000000 MHz ;</t>
+  </si>
+  <si>
+    <t>FREQUENCY NET "slv_com_top_inst.CLK2A" 115.000000 MHz ;</t>
+  </si>
+  <si>
+    <t>FREQUENCY NET "slv_com_top_inst.CLK2" 100.000000 MHz ;</t>
+  </si>
+  <si>
+    <t>FREQUENCY NET "slv_com_top_inst.CLK2A" 100.000000 MHz ;</t>
+  </si>
+  <si>
+    <r>
+      <t>LPFコメント更新</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: Section 1のガードバンドに関するコメント（299行）を更新し、115MHz→100MHzに戻した理由を記載</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>{p:PORT}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>{n:SIGNAL_t}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. CD134エラー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: 3件 → 0件になること</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. MT420/MT529警告</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: 10件 → 0件（または大幅減少）になること</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>{n:SIGNAL_t}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> が効かない場合は代替構文を試行</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. CLKCOM_OUT制約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: 100MHz制約でsetup/hold共にPASSすること</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4. Hold違反</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: 4件 → 0件になること（115MHz緩和による改善）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>5. SLICE使用率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: 89%から低下していること</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>6. 既存の修正が壊れていないこと</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>No1~9の確認</t>
+    <rPh sb="6" eb="8">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FDCファイルがDiamondプロジェクトに未登録</t>
+  </si>
+  <si>
+    <t>修正履歴 No.1〜9 コンパイル結果検証レポート</t>
+  </si>
+  <si>
+    <t>コンパイル日時: 2026-02-28 (SP0557_SP0557.srr / SP0557_SP0557.twr)</t>
+  </si>
+  <si>
+    <t>全体結果サマリ</t>
+  </si>
+  <si>
+    <t>区分</t>
+  </si>
+  <si>
+    <t>コンパイルエラー</t>
+  </si>
+  <si>
+    <t>Setupタイミング違反</t>
+  </si>
+  <si>
+    <t>Holdタイミング違反</t>
+  </si>
+  <si>
+    <t>合成ワーニング</t>
+  </si>
+  <si>
+    <t>272件</t>
+  </si>
+  <si>
+    <t>修正No.9で計画した4つの修正の適用状況</t>
+  </si>
+  <si>
+    <t>修正1: CD134 識別子エラー修正（3件） → 適用済み・効果あり</t>
+  </si>
+  <si>
+    <t>ソース状態</t>
+  </si>
+  <si>
+    <t>コンパイル反映</t>
+  </si>
+  <si>
+    <t>ppmc_ctrl.vhd:133-136</t>
+  </si>
+  <si>
+    <t>ENB_START syn_preserve削除</t>
+  </si>
+  <si>
+    <t>適用済み</t>
+  </si>
+  <si>
+    <t>dec6b_5b.vhd:36-37</t>
+  </si>
+  <si>
+    <t>DATAOUT syn_preserve削除</t>
+  </si>
+  <si>
+    <t>slv_rx_ctrl.vhd:90-93</t>
+  </si>
+  <si>
+    <t>NODE syn_preserve削除</t>
+  </si>
+  <si>
+    <t>s_pls_ld / byte_cnt の属性も正しく保持されています。</t>
+  </si>
+  <si>
+    <t>修正2: MT420/MT529 PLL クロック制約修正 → ソース適用済みだがコンパイル未反映（致命的）</t>
+  </si>
+  <si>
+    <t>問題: FDCファイルがSynplifyに読み込まれていない</t>
+  </si>
+  <si>
+    <t>合成レポート 1240行目:</t>
+  </si>
+  <si>
+    <t>@A: MF827 |No constraint file specified.</t>
+  </si>
+  <si>
+    <t>Removed file: C:\FPGA work\PCBNo.10081\FPGA\RTL\IPcore\pll_gen\pll_gen.fdc</t>
+  </si>
+  <si>
+    <t>Removed file: C:\FPGA work\PCBNo.10081\FPGA\SP0557\SP0557.fdc</t>
+  </si>
+  <si>
+    <t>@W: MT420 |Found inferred clock pll_gen|CLKOS2_inferred_clock with period 5.00ns</t>
+  </si>
+  <si>
+    <t>@W: MT420 |Found inferred clock SP0557|CLK20M with period 5.00ns</t>
+  </si>
+  <si>
+    <t>@W: MT420 |Found inferred clock pll_gen|CLKOS_inferred_clock with period 5.00ns</t>
+  </si>
+  <si>
+    <t>@W: MT420 |Found inferred clock pll_gen|CLKOP_inferred_clock with period 5.00ns</t>
+  </si>
+  <si>
+    <t>@W: MT420 |Found inferred clock pll_gen|CLKOS3_inferred_clock with period 5.00ns</t>
+  </si>
+  <si>
+    <t>全PLLクロックがデフォルト200MHz (5ns)として推定され、FDCのclock group/multicycle/false path制約も全て無効です。</t>
+  </si>
+  <si>
+    <t>修正3: CLKCOM_OUT タイミング違反修正 → 一部適用だが主要制約が未反映（致命的）</t>
+  </si>
+  <si>
+    <t>UP_TXD SLEWRATE=FAST</t>
+  </si>
+  <si>
+    <t>FREQUENCY PORT "UP_CLK" 20MHz</t>
+  </si>
+  <si>
+    <t>FREQUENCY NET制約 (5クロック)</t>
+  </si>
+  <si>
+    <t>適用済み・反映あり</t>
+  </si>
+  <si>
+    <t>BLOCK PATH CLK20M_c &lt;-&gt; s_PLL_CLK20M/CLK1</t>
+  </si>
+  <si>
+    <t>MULTICYCLE s_PLL_CLK20M &lt;-&gt; CLK1 (2X)</t>
+  </si>
+  <si>
+    <t>問題: LPFのクロックネット名が実際のPAR認識名と不一致</t>
+  </si>
+  <si>
+    <t>LPF記述</t>
+  </si>
+  <si>
+    <t>PARが認識する実際のネット名</t>
+  </si>
+  <si>
+    <t>slv_com_top_inst.CLK2</t>
+  </si>
+  <si>
+    <t>slv_com_top_inst.CLKCOM_OUT</t>
+  </si>
+  <si>
+    <t>不一致</t>
+  </si>
+  <si>
+    <t>slv_com_top_inst.CLK2A</t>
+  </si>
+  <si>
+    <t>LPF Section</t>
+  </si>
+  <si>
+    <t>制約</t>
+  </si>
+  <si>
+    <t>影響</t>
+  </si>
+  <si>
+    <t>Section 2 (一部)</t>
+  </si>
+  <si>
+    <t>BLOCK PATH CLK20M_c &lt;-&gt; CLK2/CLK2A</t>
+  </si>
+  <si>
+    <t>CLK20M_c→CLKCOM_OUT/CLK2Aパスが解析対象に残存</t>
+  </si>
+  <si>
+    <t>Section 4</t>
+  </si>
+  <si>
+    <t>BLOCK PATH s_PLL_CLK20M &lt;-&gt; CLK2/CLK2A</t>
+  </si>
+  <si>
+    <t>20MHz↔100MHzパスが未遮断</t>
+  </si>
+  <si>
+    <t>Section 5</t>
+  </si>
+  <si>
+    <t>MULTICYCLE CLK1 &lt;-&gt; CLK2 (10X/2X)</t>
+  </si>
+  <si>
+    <t>59パスが100MHz解析下に残存（最大の問題）</t>
+  </si>
+  <si>
+    <t>Section 6</t>
+  </si>
+  <si>
+    <t>MULTICYCLE CLK1 &lt;-&gt; CLK2A (10X/2X)</t>
+  </si>
+  <si>
+    <t>CLK1↔CLK2Aパスが緩和されず</t>
+  </si>
+  <si>
+    <t>TWR（タイミングレポート）で確認した証拠:</t>
+  </si>
+  <si>
+    <t>タイミング結果詳細 (TWR)</t>
+  </si>
+  <si>
+    <t>クロックドメイン</t>
+  </si>
+  <si>
+    <t>実測</t>
+  </si>
+  <si>
+    <t>スラック</t>
+  </si>
+  <si>
+    <t>100.000 MHz</t>
+  </si>
+  <si>
+    <t>98.483 MHz</t>
+  </si>
+  <si>
+    <t>-0.154ns</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>CLK2A (100MHz)</t>
+  </si>
+  <si>
+    <t>271.370 MHz</t>
+  </si>
+  <si>
+    <t>+6.315ns</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>20.000 MHz</t>
+  </si>
+  <si>
+    <t>67.645 MHz</t>
+  </si>
+  <si>
+    <t>充分</t>
+  </si>
+  <si>
+    <t>CLK1 (10MHz)</t>
+  </si>
+  <si>
+    <t>10.000 MHz</t>
+  </si>
+  <si>
+    <t>14.067 MHz</t>
+  </si>
+  <si>
+    <t>UP_CLK_c (20MHz)</t>
+  </si>
+  <si>
+    <t>(パスなし)</t>
+  </si>
+  <si>
+    <t>必要な修正アクション</t>
+  </si>
+  <si>
+    <t>アクション1 (最優先): SP0557.ldfにFDCファイルを登録</t>
+  </si>
+  <si>
+    <t>これにより:</t>
+  </si>
+  <si>
+    <t>MT420/MT529ワーニングが解消</t>
+  </si>
+  <si>
+    <t>PLLクロックが正しい周波数で合成最適化される</t>
+  </si>
+  <si>
+    <t>FDCのmulticycle/false path制約がSynplify合成時に有効化される</t>
+  </si>
+  <si>
+    <t>アクション2 (最優先): LPFクロックネット名の修正</t>
+  </si>
+  <si>
+    <t># 修正前                                    # 修正後</t>
+  </si>
+  <si>
+    <t>"slv_com_top_inst.CLK2"                  → "slv_com_top_inst.CLKCOM_OUT"</t>
+  </si>
+  <si>
+    <t>"slv_com_top_inst.CLK2A"                 → "slv_com_top_inst/CLK2A"</t>
+  </si>
+  <si>
+    <t>LPF Section 2, 4, 5, 6 の全8箇所を修正する必要があります。</t>
+  </si>
+  <si>
+    <t>CLK1↔CLKCOM_OUT の59+23パスにMULTICYCLE制約が適用</t>
+  </si>
+  <si>
+    <t>CLKCOM_OUTのタイミング違反が解消される可能性が高い（ルーティング資源の解放）</t>
+  </si>
+  <si>
+    <t>まとめ</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>RTLソース</t>
+  </si>
+  <si>
+    <t>タイミング制約新規作成 (LPF)</t>
+  </si>
+  <si>
+    <t>✓ 適用済み</t>
+  </si>
+  <si>
+    <t>S3IO CLK制約追加 (LPF)</t>
+  </si>
+  <si>
+    <t>RTLデッドコード削除</t>
+  </si>
+  <si>
+    <t>✓ 反映済み</t>
+  </si>
+  <si>
+    <t>(No1-3分析)</t>
+  </si>
+  <si>
+    <t>ワーニング削除 (RTL+FDC)</t>
+  </si>
+  <si>
+    <t>FDC未読込のため一部未反映</t>
+  </si>
+  <si>
+    <t>S3IO通信異常調査</t>
+  </si>
+  <si>
+    <t>✓ 反映済み（LPF部分）</t>
+  </si>
+  <si>
+    <t>No6追加解析</t>
+  </si>
+  <si>
+    <t>ワーニング増加原因解消</t>
+  </si>
+  <si>
+    <t>9-修正1</t>
+  </si>
+  <si>
+    <t>CD134エラー修正</t>
+  </si>
+  <si>
+    <t>✓ 完全反映</t>
+  </si>
+  <si>
+    <t>9-修正2</t>
+  </si>
+  <si>
+    <t>MT420/MT529修正</t>
+  </si>
+  <si>
+    <t>9-修正3</t>
+  </si>
+  <si>
+    <t>CLKCOM_OUTタイミング修正</t>
+  </si>
+  <si>
+    <t>この2点を修正して再コンパイルすれば、FDC制約とLPFタイミング制約が全て有効化され、CLKCOM_OUTのタイミング違反解消が期待できます。修正しますか？</t>
+  </si>
+  <si>
+    <t>Updated todo list tracking modification history and synthesis report review tasks</t>
+  </si>
+  <si>
+    <t>Update Todos</t>
+  </si>
+  <si>
+    <t> Read modification history (修正履歴.xlsx) - items No.1-9</t>
+  </si>
+  <si>
+    <t> Read synthesis report (SP0557_SP0557.srr) for errors/warnings</t>
+  </si>
+  <si>
+    <t> Read place &amp; route / timing reports for MAP/PAR results</t>
+  </si>
+  <si>
+    <t> Verify RTL source files contain the expected changes from No.9 sheet</t>
+  </si>
+  <si>
+    <t> Verify pll_gen.fdc is being loaded by synthesis and check why MT420/MT529 remain</t>
+  </si>
+  <si>
+    <t> Compare previous vs current warning counts</t>
+  </si>
+  <si>
+    <t> Report verification results</t>
+  </si>
+  <si>
+    <t>これはdiamondツール上で実施する手順ではないのですか</t>
+  </si>
+  <si>
+    <t>はい、その通りです。</t>
+  </si>
+  <si>
+    <t>Diamond上での操作手順</t>
+  </si>
+  <si>
+    <t>3. 以下の2ファイルを追加:</t>
+  </si>
+  <si>
+    <t>5. 保存してから再合成（Synthesize）を実行</t>
+  </si>
+  <si>
+    <t>残りの問題: LPFクロックネット名の修正</t>
+  </si>
+  <si>
+    <t>修正前</t>
+  </si>
+  <si>
+    <t>修正後</t>
+  </si>
+  <si>
+    <t>"slv_com_top_inst.CLK2"</t>
+  </si>
+  <si>
+    <t>"slv_com_top_inst.CLKCOM_OUT"</t>
+  </si>
+  <si>
+    <t>"slv_com_top_inst.CLK2A"</t>
+  </si>
+  <si>
+    <t>"slv_com_top_inst/CLK2A"</t>
+  </si>
+  <si>
+    <t>&lt;Source name="RTL/IPcore/pll_gen/pll_gen.fdc" type="FDC" type_short="FDC"&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    &lt;Options/&gt;</t>
+  </si>
+  <si>
+    <t>&lt;/Source&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Source name="SP0557/SP0557.fdc" type="FDC" type_short="FDC"&gt;</t>
+  </si>
+  <si>
+    <t>pll_gen.fdc の内容は正しく修正されています:</t>
+  </si>
+  <si>
+    <t>{p:CLKOP} → {n:CLKOP_t} ✓</t>
+  </si>
+  <si>
+    <t>{p:CLKOS} → {n:CLKOS_t} ✓</t>
+  </si>
+  <si>
+    <t>{p:CLKOS2} → {n:CLKOS2_t} ✓</t>
+  </si>
+  <si>
+    <t>{p:CLKOS3} → {n:CLKOS3_t} ✓</t>
+  </si>
+  <si>
+    <t>全クロックが -clockgroup pll_clks で統一 ✓</t>
+  </si>
+  <si>
+    <t>stdout.log にFDCファイル削除の記録:</t>
+  </si>
+  <si>
+    <t>slv_com_top_inst/CLK2A (.ではなく/)</t>
+  </si>
+  <si>
+    <t>CLK1→CLKCOM_OUT: 59パスがFREQUENCY NET "slv_com_top_inst.CLKCOM_OUT" 100MHzで解析（MULTICYCLEなし）</t>
+  </si>
+  <si>
+    <t>CLKCOM_OUT→CLK1: 23パスがFREQUENCY NET "slv_com_top_inst.CLK1" 10MHzで解析（MULTICYCLEなし）</t>
+  </si>
+  <si>
+    <t>Hold違反: CLK1ドメインで -0.321ns（s_LRSTb_r44, TX_RSTb_i_r8）</t>
+  </si>
+  <si>
+    <t>SP0557.ldf に以下の2行を追加する必要があります:</t>
+  </si>
+  <si>
+    <t>こちらは .lpf ファイルのテキスト修正なので、Diamond上でもテキストエディタでもどちらでも対応可能です。修正箇所は以下の通りです:</t>
+  </si>
+  <si>
+    <r>
+      <t>0件</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> (合成成功)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1件</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> (CLKCOM_OUT: 98.483MHz &lt; 100MHz)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1件</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> (CLK1: -0.321ns)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CD134エラー </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>0件</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>根本原因</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: SP0557.ldf（Diamondプロジェクトファイル）に pll_gen.fdc と SP0557.fdc が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ソースとして登録されていない</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>。VHDLファイルとLPFファイルのみが登録されています。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>結果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: MT420/MT529ワーニングが</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>5件とも残存</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>適用済み</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> (LPF 66行目)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>適用済み</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> (LPF 362行目)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>これにより以下の制約が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>全て無視</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>されています:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>これが</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>CLKCOM_OUTタイミング違反の直接原因</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>です（98.483MHz &lt; 100MHz）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>一部のみ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> (ネット名不一致で制約無視)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>一部のみ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> (同上)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>✗ 未反映</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> (LDFにFDC未登録)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>✗ 未反映</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> (ネット名不一致)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>結論</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: RTLソースコードの修正は全て正しく適用されていますが、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>2つの設定上の問題</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>により、コンパイル結果には完全に反映されていません。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. FDCファイルがDiamondプロジェクトに未登録</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> → MT420/MT529残存</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. LPFのクロックネット名不一致</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> (CLK2 ≠ CLKCOM_OUT, .CLK2A ≠ /CLK2A) → MULTICYCLE/BLOCK PATH制約が無視されタイミング違反継続</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SP0557.ldf はDiamond GUIで管理されるプロジェクトファイルなので、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>FDCファイルの登録はDiamond上で行うのが正しい手順</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>です。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. Diamond</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>でプロジェクト SP0557.ldf を開く</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. File List</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> パネルで右クリック → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>Add</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>Existing File...</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4. ファイルタイプが </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>FDC (Synplify Forward Declaration Constraint)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> として認識されていることを確認</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>.ldf をテキストエディタで直接編集しても動作はしますが、Diamondが管理するXML構造なので、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>Diamond GUI上で追加する方が安全</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>です。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>LPF内の </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>Section 2, 4, 5, 6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> の計8箇所が対象です。こちらの修正は私の方で実施できますが、対応しますか？</t>
+    </r>
+  </si>
+  <si>
+    <t>11</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>No1~10の確認</t>
+    <rPh sb="7" eb="9">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="30">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5786,16 +7431,32 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <name val="Meiryo UI"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Meiryo UI"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -5862,7 +7523,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6112,20 +7773,47 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6586,21 +8274,39 @@
       <c r="F12" s="26"/>
     </row>
     <row r="13" spans="3:6">
-      <c r="C13" s="26"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="27"/>
+      <c r="C13" s="26">
+        <v>9</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>752</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>753</v>
+      </c>
       <c r="F13" s="26"/>
     </row>
     <row r="14" spans="3:6">
-      <c r="C14" s="26"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="27"/>
+      <c r="C14" s="26">
+        <v>10</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>836</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>837</v>
+      </c>
       <c r="F14" s="26"/>
     </row>
     <row r="15" spans="3:6">
-      <c r="C15" s="26"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="27"/>
+      <c r="C15" s="26">
+        <v>11</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>1020</v>
+      </c>
       <c r="F15" s="26"/>
     </row>
     <row r="16" spans="3:6">
@@ -6706,6 +8412,2165 @@
       <c r="F32" s="26"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14089E9A-DD6C-474E-BC76-1DCDCF7A2A9D}">
+  <dimension ref="A1:B181"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="24">
+      <c r="A1" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="24">
+      <c r="A7" s="14" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="18.75">
+      <c r="A9" s="15" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="18.75">
+      <c r="A13" s="15" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="17" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="18"/>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="18" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="24" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="18" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="16" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="16" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="16" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="1" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="16" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="16" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="16" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="17" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="18"/>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="18" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="18" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="16" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="16" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="1" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="16" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="17" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="18"/>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="18" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="24" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="18" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="1" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="16" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="16" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="16" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="16" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="1" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="16" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="16" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="16" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="16" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="16" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="16" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="16" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="16" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="16" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="16" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="16" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="16" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="16" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="16" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="16" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="16" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="16" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="16" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="16" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="16" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="16" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="16" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="16" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="16" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="16" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="16" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="16" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="16" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="16" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="16" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="16" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="16" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="16" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="16" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="16" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="16" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="16" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" s="16" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="16" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="16" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="16" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" s="16" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" s="16" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" s="16" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" s="16" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" s="16" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="16" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" s="17" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" ht="24">
+      <c r="A145" s="14" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" ht="18.75">
+      <c r="A147" s="15" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="1" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" s="18"/>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" s="18" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" s="18" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" s="18" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" s="1" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" ht="24">
+      <c r="A159" s="14" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="B161" s="20" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" ht="71.25">
+      <c r="A162" s="21" t="s">
+        <v>772</v>
+      </c>
+      <c r="B162" s="9" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" ht="71.25">
+      <c r="A163" s="21" t="s">
+        <v>774</v>
+      </c>
+      <c r="B163" s="9" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" ht="71.25">
+      <c r="A164" s="21" t="s">
+        <v>776</v>
+      </c>
+      <c r="B164" s="9" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" ht="60">
+      <c r="A165" s="21" t="s">
+        <v>778</v>
+      </c>
+      <c r="B165" s="21" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" ht="47.25">
+      <c r="A166" s="21" t="s">
+        <v>779</v>
+      </c>
+      <c r="B166" s="9" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" ht="24">
+      <c r="A169" s="14" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="1" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="18"/>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="19" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="19" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="88" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="19" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" s="19" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" s="19" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" s="19" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" s="25" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" s="25" t="s">
+        <v>783</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80AF1D6C-FC01-45A2-8677-95498AA084BB}">
+  <dimension ref="A1:E149"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="77.75" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="5" max="5" width="7.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A1" s="89" t="s">
+        <v>839</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+    </row>
+    <row r="2" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A2" s="74" t="s">
+        <v>840</v>
+      </c>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+    </row>
+    <row r="3" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A3" s="72"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+    </row>
+    <row r="4" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A4" s="89" t="s">
+        <v>841</v>
+      </c>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+    </row>
+    <row r="5" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A5" s="91" t="s">
+        <v>842</v>
+      </c>
+      <c r="B5" s="92" t="s">
+        <v>557</v>
+      </c>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+    </row>
+    <row r="6" spans="1:5" s="90" customFormat="1" ht="20.25" thickBot="1">
+      <c r="A6" s="79" t="s">
+        <v>843</v>
+      </c>
+      <c r="B6" s="93" t="s">
+        <v>996</v>
+      </c>
+      <c r="C6" s="72"/>
+      <c r="D6" s="72"/>
+      <c r="E6" s="72"/>
+    </row>
+    <row r="7" spans="1:5" s="90" customFormat="1" ht="33.75" thickBot="1">
+      <c r="A7" s="79" t="s">
+        <v>844</v>
+      </c>
+      <c r="B7" s="93" t="s">
+        <v>997</v>
+      </c>
+      <c r="C7" s="72"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
+    </row>
+    <row r="8" spans="1:5" s="90" customFormat="1" ht="20.25" thickBot="1">
+      <c r="A8" s="79" t="s">
+        <v>845</v>
+      </c>
+      <c r="B8" s="93" t="s">
+        <v>998</v>
+      </c>
+      <c r="C8" s="72"/>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
+    </row>
+    <row r="9" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A9" s="79" t="s">
+        <v>846</v>
+      </c>
+      <c r="B9" s="89" t="s">
+        <v>847</v>
+      </c>
+      <c r="C9" s="72"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72"/>
+    </row>
+    <row r="10" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A10" s="72"/>
+      <c r="B10" s="72"/>
+      <c r="C10" s="72"/>
+      <c r="D10" s="72"/>
+      <c r="E10" s="72"/>
+    </row>
+    <row r="11" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A11" s="89" t="s">
+        <v>848</v>
+      </c>
+      <c r="B11" s="72"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="72"/>
+      <c r="E11" s="72"/>
+    </row>
+    <row r="12" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A12" s="89" t="s">
+        <v>849</v>
+      </c>
+      <c r="B12" s="72"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+    </row>
+    <row r="13" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A13" s="91" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="91" t="s">
+        <v>658</v>
+      </c>
+      <c r="C13" s="91" t="s">
+        <v>850</v>
+      </c>
+      <c r="D13" s="92" t="s">
+        <v>851</v>
+      </c>
+      <c r="E13" s="72"/>
+    </row>
+    <row r="14" spans="1:5" s="90" customFormat="1" ht="33.75" thickBot="1">
+      <c r="A14" s="79" t="s">
+        <v>852</v>
+      </c>
+      <c r="B14" s="79" t="s">
+        <v>853</v>
+      </c>
+      <c r="C14" s="94" t="s">
+        <v>854</v>
+      </c>
+      <c r="D14" s="81" t="s">
+        <v>999</v>
+      </c>
+      <c r="E14" s="72"/>
+    </row>
+    <row r="15" spans="1:5" s="90" customFormat="1" ht="33.75" thickBot="1">
+      <c r="A15" s="79" t="s">
+        <v>855</v>
+      </c>
+      <c r="B15" s="79" t="s">
+        <v>856</v>
+      </c>
+      <c r="C15" s="94" t="s">
+        <v>854</v>
+      </c>
+      <c r="D15" s="81" t="s">
+        <v>999</v>
+      </c>
+      <c r="E15" s="72"/>
+    </row>
+    <row r="16" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A16" s="79" t="s">
+        <v>857</v>
+      </c>
+      <c r="B16" s="79" t="s">
+        <v>858</v>
+      </c>
+      <c r="C16" s="94" t="s">
+        <v>854</v>
+      </c>
+      <c r="D16" s="74" t="s">
+        <v>999</v>
+      </c>
+      <c r="E16" s="72"/>
+    </row>
+    <row r="17" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A17" s="74" t="s">
+        <v>859</v>
+      </c>
+      <c r="B17" s="72"/>
+      <c r="C17" s="72"/>
+      <c r="D17" s="72"/>
+      <c r="E17" s="72"/>
+    </row>
+    <row r="18" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A18" s="72"/>
+      <c r="B18" s="72"/>
+      <c r="C18" s="72"/>
+      <c r="D18" s="72"/>
+      <c r="E18" s="72"/>
+    </row>
+    <row r="19" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A19" s="89" t="s">
+        <v>860</v>
+      </c>
+      <c r="B19" s="72"/>
+      <c r="C19" s="72"/>
+      <c r="D19" s="72"/>
+      <c r="E19" s="72"/>
+    </row>
+    <row r="20" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A20" s="74" t="s">
+        <v>983</v>
+      </c>
+      <c r="B20" s="72"/>
+      <c r="C20" s="72"/>
+      <c r="D20" s="72"/>
+      <c r="E20" s="72"/>
+    </row>
+    <row r="21" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A21" s="75"/>
+      <c r="B21" s="72"/>
+      <c r="C21" s="72"/>
+      <c r="D21" s="72"/>
+      <c r="E21" s="72"/>
+    </row>
+    <row r="22" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A22" s="75" t="s">
+        <v>984</v>
+      </c>
+      <c r="B22" s="72"/>
+      <c r="C22" s="72"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+    </row>
+    <row r="23" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A23" s="75" t="s">
+        <v>985</v>
+      </c>
+      <c r="B23" s="72"/>
+      <c r="C23" s="72"/>
+      <c r="D23" s="72"/>
+      <c r="E23" s="72"/>
+    </row>
+    <row r="24" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A24" s="75" t="s">
+        <v>986</v>
+      </c>
+      <c r="B24" s="72"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+    </row>
+    <row r="25" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A25" s="75" t="s">
+        <v>987</v>
+      </c>
+      <c r="B25" s="72"/>
+      <c r="C25" s="72"/>
+      <c r="D25" s="72"/>
+      <c r="E25" s="72"/>
+    </row>
+    <row r="26" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A26" s="75" t="s">
+        <v>988</v>
+      </c>
+      <c r="B26" s="72"/>
+      <c r="C26" s="72"/>
+      <c r="D26" s="72"/>
+      <c r="E26" s="72"/>
+    </row>
+    <row r="27" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A27" s="74"/>
+      <c r="B27" s="72"/>
+      <c r="C27" s="72"/>
+      <c r="D27" s="72"/>
+      <c r="E27" s="72"/>
+    </row>
+    <row r="28" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A28" s="89" t="s">
+        <v>861</v>
+      </c>
+      <c r="B28" s="72"/>
+      <c r="C28" s="72"/>
+      <c r="D28" s="72"/>
+      <c r="E28" s="72"/>
+    </row>
+    <row r="29" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A29" s="74" t="s">
+        <v>862</v>
+      </c>
+      <c r="B29" s="72"/>
+      <c r="C29" s="72"/>
+      <c r="D29" s="72"/>
+      <c r="E29" s="72"/>
+    </row>
+    <row r="30" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A30" s="72" t="s">
+        <v>863</v>
+      </c>
+      <c r="B30" s="72"/>
+      <c r="C30" s="72"/>
+      <c r="D30" s="72"/>
+      <c r="E30" s="72"/>
+    </row>
+    <row r="31" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A31" s="74" t="s">
+        <v>989</v>
+      </c>
+      <c r="B31" s="72"/>
+      <c r="C31" s="72"/>
+      <c r="D31" s="72"/>
+      <c r="E31" s="72"/>
+    </row>
+    <row r="32" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A32" s="72" t="s">
+        <v>864</v>
+      </c>
+      <c r="B32" s="72"/>
+      <c r="C32" s="72"/>
+      <c r="D32" s="72"/>
+      <c r="E32" s="72"/>
+    </row>
+    <row r="33" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A33" s="72" t="s">
+        <v>865</v>
+      </c>
+      <c r="B33" s="72"/>
+      <c r="C33" s="72"/>
+      <c r="D33" s="72"/>
+      <c r="E33" s="72"/>
+    </row>
+    <row r="34" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A34" s="89" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B34" s="72"/>
+      <c r="C34" s="72"/>
+      <c r="D34" s="72"/>
+      <c r="E34" s="72"/>
+    </row>
+    <row r="35" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A35" s="89" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B35" s="72"/>
+      <c r="C35" s="72"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="72"/>
+    </row>
+    <row r="36" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A36" s="72" t="s">
+        <v>866</v>
+      </c>
+      <c r="B36" s="72"/>
+      <c r="C36" s="72"/>
+      <c r="D36" s="72"/>
+      <c r="E36" s="72"/>
+    </row>
+    <row r="37" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A37" s="72" t="s">
+        <v>867</v>
+      </c>
+      <c r="B37" s="72"/>
+      <c r="C37" s="72"/>
+      <c r="D37" s="72"/>
+      <c r="E37" s="72"/>
+    </row>
+    <row r="38" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A38" s="72" t="s">
+        <v>868</v>
+      </c>
+      <c r="B38" s="72"/>
+      <c r="C38" s="72"/>
+      <c r="D38" s="72"/>
+      <c r="E38" s="72"/>
+    </row>
+    <row r="39" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A39" s="72" t="s">
+        <v>869</v>
+      </c>
+      <c r="B39" s="72"/>
+      <c r="C39" s="72"/>
+      <c r="D39" s="72"/>
+      <c r="E39" s="72"/>
+    </row>
+    <row r="40" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A40" s="72" t="s">
+        <v>870</v>
+      </c>
+      <c r="B40" s="72"/>
+      <c r="C40" s="72"/>
+      <c r="D40" s="72"/>
+      <c r="E40" s="72"/>
+    </row>
+    <row r="41" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A41" s="74" t="s">
+        <v>871</v>
+      </c>
+      <c r="B41" s="72"/>
+      <c r="C41" s="72"/>
+      <c r="D41" s="72"/>
+      <c r="E41" s="72"/>
+    </row>
+    <row r="42" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A42" s="72"/>
+      <c r="B42" s="72"/>
+      <c r="C42" s="72"/>
+      <c r="D42" s="72"/>
+      <c r="E42" s="72"/>
+    </row>
+    <row r="43" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A43" s="89" t="s">
+        <v>872</v>
+      </c>
+      <c r="B43" s="72"/>
+      <c r="C43" s="72"/>
+      <c r="D43" s="72"/>
+      <c r="E43" s="72"/>
+    </row>
+    <row r="44" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A44" s="91" t="s">
+        <v>70</v>
+      </c>
+      <c r="B44" s="92" t="s">
+        <v>71</v>
+      </c>
+      <c r="C44" s="72"/>
+      <c r="D44" s="72"/>
+      <c r="E44" s="72"/>
+    </row>
+    <row r="45" spans="1:5" s="90" customFormat="1" ht="20.25" thickBot="1">
+      <c r="A45" s="79" t="s">
+        <v>873</v>
+      </c>
+      <c r="B45" s="93" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C45" s="72"/>
+      <c r="D45" s="72"/>
+      <c r="E45" s="72"/>
+    </row>
+    <row r="46" spans="1:5" s="90" customFormat="1" ht="20.25" thickBot="1">
+      <c r="A46" s="79" t="s">
+        <v>874</v>
+      </c>
+      <c r="B46" s="93" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C46" s="72"/>
+      <c r="D46" s="72"/>
+      <c r="E46" s="72"/>
+    </row>
+    <row r="47" spans="1:5" s="90" customFormat="1" ht="20.25" thickBot="1">
+      <c r="A47" s="79" t="s">
+        <v>875</v>
+      </c>
+      <c r="B47" s="93" t="s">
+        <v>876</v>
+      </c>
+      <c r="C47" s="72"/>
+      <c r="D47" s="72"/>
+      <c r="E47" s="72"/>
+    </row>
+    <row r="48" spans="1:5" s="90" customFormat="1" ht="20.25" thickBot="1">
+      <c r="A48" s="79" t="s">
+        <v>877</v>
+      </c>
+      <c r="B48" s="93" t="s">
+        <v>876</v>
+      </c>
+      <c r="C48" s="72"/>
+      <c r="D48" s="72"/>
+      <c r="E48" s="72"/>
+    </row>
+    <row r="49" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A49" s="79" t="s">
+        <v>878</v>
+      </c>
+      <c r="B49" s="89" t="s">
+        <v>876</v>
+      </c>
+      <c r="C49" s="72"/>
+      <c r="D49" s="72"/>
+      <c r="E49" s="72"/>
+    </row>
+    <row r="50" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A50" s="89" t="s">
+        <v>879</v>
+      </c>
+      <c r="B50" s="72"/>
+      <c r="C50" s="72"/>
+      <c r="D50" s="72"/>
+      <c r="E50" s="72"/>
+    </row>
+    <row r="51" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A51" s="91" t="s">
+        <v>880</v>
+      </c>
+      <c r="B51" s="91" t="s">
+        <v>881</v>
+      </c>
+      <c r="C51" s="92" t="s">
+        <v>71</v>
+      </c>
+      <c r="D51" s="72"/>
+      <c r="E51" s="72"/>
+    </row>
+    <row r="52" spans="1:5" s="90" customFormat="1" ht="33.75" thickBot="1">
+      <c r="A52" s="79" t="s">
+        <v>882</v>
+      </c>
+      <c r="B52" s="79" t="s">
+        <v>883</v>
+      </c>
+      <c r="C52" s="93" t="s">
+        <v>884</v>
+      </c>
+      <c r="D52" s="72"/>
+      <c r="E52" s="72"/>
+    </row>
+    <row r="53" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A53" s="79" t="s">
+        <v>885</v>
+      </c>
+      <c r="B53" s="79" t="s">
+        <v>990</v>
+      </c>
+      <c r="C53" s="89" t="s">
+        <v>884</v>
+      </c>
+      <c r="D53" s="72"/>
+      <c r="E53" s="72"/>
+    </row>
+    <row r="54" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A54" s="74" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B54" s="72"/>
+      <c r="C54" s="72"/>
+      <c r="D54" s="72"/>
+      <c r="E54" s="72"/>
+    </row>
+    <row r="55" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A55" s="91" t="s">
+        <v>886</v>
+      </c>
+      <c r="B55" s="91" t="s">
+        <v>887</v>
+      </c>
+      <c r="C55" s="92" t="s">
+        <v>888</v>
+      </c>
+      <c r="D55" s="72"/>
+      <c r="E55" s="72"/>
+    </row>
+    <row r="56" spans="1:5" s="90" customFormat="1" ht="132.75" thickBot="1">
+      <c r="A56" s="79" t="s">
+        <v>889</v>
+      </c>
+      <c r="B56" s="79" t="s">
+        <v>890</v>
+      </c>
+      <c r="C56" s="81" t="s">
+        <v>891</v>
+      </c>
+      <c r="D56" s="72"/>
+      <c r="E56" s="72"/>
+    </row>
+    <row r="57" spans="1:5" s="90" customFormat="1" ht="83.25" thickBot="1">
+      <c r="A57" s="79" t="s">
+        <v>892</v>
+      </c>
+      <c r="B57" s="79" t="s">
+        <v>893</v>
+      </c>
+      <c r="C57" s="81" t="s">
+        <v>894</v>
+      </c>
+      <c r="D57" s="72"/>
+      <c r="E57" s="72"/>
+    </row>
+    <row r="58" spans="1:5" s="90" customFormat="1" ht="99.75" thickBot="1">
+      <c r="A58" s="94" t="s">
+        <v>895</v>
+      </c>
+      <c r="B58" s="94" t="s">
+        <v>896</v>
+      </c>
+      <c r="C58" s="93" t="s">
+        <v>897</v>
+      </c>
+      <c r="D58" s="72"/>
+      <c r="E58" s="72"/>
+    </row>
+    <row r="59" spans="1:5" s="90" customFormat="1" ht="66">
+      <c r="A59" s="79" t="s">
+        <v>898</v>
+      </c>
+      <c r="B59" s="79" t="s">
+        <v>899</v>
+      </c>
+      <c r="C59" s="74" t="s">
+        <v>900</v>
+      </c>
+      <c r="D59" s="72"/>
+      <c r="E59" s="72"/>
+    </row>
+    <row r="60" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A60" s="89" t="s">
+        <v>901</v>
+      </c>
+      <c r="B60" s="72"/>
+      <c r="C60" s="72"/>
+      <c r="D60" s="72"/>
+      <c r="E60" s="72"/>
+    </row>
+    <row r="61" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A61" s="74" t="s">
+        <v>991</v>
+      </c>
+      <c r="B61" s="72"/>
+      <c r="C61" s="72"/>
+      <c r="D61" s="72"/>
+      <c r="E61" s="72"/>
+    </row>
+    <row r="62" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A62" s="74" t="s">
+        <v>992</v>
+      </c>
+      <c r="B62" s="72"/>
+      <c r="C62" s="72"/>
+      <c r="D62" s="72"/>
+      <c r="E62" s="72"/>
+    </row>
+    <row r="63" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A63" s="74" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B63" s="72"/>
+      <c r="C63" s="72"/>
+      <c r="D63" s="72"/>
+      <c r="E63" s="72"/>
+    </row>
+    <row r="64" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A64" s="72"/>
+      <c r="B64" s="72"/>
+      <c r="C64" s="72"/>
+      <c r="D64" s="72"/>
+      <c r="E64" s="72"/>
+    </row>
+    <row r="65" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A65" s="89" t="s">
+        <v>902</v>
+      </c>
+      <c r="B65" s="72"/>
+      <c r="C65" s="72"/>
+      <c r="D65" s="72"/>
+      <c r="E65" s="72"/>
+    </row>
+    <row r="66" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A66" s="91" t="s">
+        <v>903</v>
+      </c>
+      <c r="B66" s="91" t="s">
+        <v>887</v>
+      </c>
+      <c r="C66" s="91" t="s">
+        <v>904</v>
+      </c>
+      <c r="D66" s="91" t="s">
+        <v>905</v>
+      </c>
+      <c r="E66" s="92" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" s="90" customFormat="1" ht="33.75" thickBot="1">
+      <c r="A67" s="79" t="s">
+        <v>95</v>
+      </c>
+      <c r="B67" s="79" t="s">
+        <v>906</v>
+      </c>
+      <c r="C67" s="79" t="s">
+        <v>907</v>
+      </c>
+      <c r="D67" s="94" t="s">
+        <v>908</v>
+      </c>
+      <c r="E67" s="93" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" s="90" customFormat="1" ht="33.75" thickBot="1">
+      <c r="A68" s="79" t="s">
+        <v>910</v>
+      </c>
+      <c r="B68" s="79" t="s">
+        <v>906</v>
+      </c>
+      <c r="C68" s="79" t="s">
+        <v>911</v>
+      </c>
+      <c r="D68" s="79" t="s">
+        <v>912</v>
+      </c>
+      <c r="E68" s="81" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" s="90" customFormat="1" ht="33.75" thickBot="1">
+      <c r="A69" s="79" t="s">
+        <v>101</v>
+      </c>
+      <c r="B69" s="79" t="s">
+        <v>914</v>
+      </c>
+      <c r="C69" s="79" t="s">
+        <v>915</v>
+      </c>
+      <c r="D69" s="79" t="s">
+        <v>916</v>
+      </c>
+      <c r="E69" s="81" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" s="90" customFormat="1" ht="33.75" thickBot="1">
+      <c r="A70" s="79" t="s">
+        <v>917</v>
+      </c>
+      <c r="B70" s="79" t="s">
+        <v>918</v>
+      </c>
+      <c r="C70" s="79" t="s">
+        <v>919</v>
+      </c>
+      <c r="D70" s="79" t="s">
+        <v>916</v>
+      </c>
+      <c r="E70" s="81" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A71" s="79" t="s">
+        <v>920</v>
+      </c>
+      <c r="B71" s="79" t="s">
+        <v>510</v>
+      </c>
+      <c r="C71" s="79" t="s">
+        <v>510</v>
+      </c>
+      <c r="D71" s="79" t="s">
+        <v>510</v>
+      </c>
+      <c r="E71" s="74" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A72" s="74" t="s">
+        <v>993</v>
+      </c>
+      <c r="B72" s="72"/>
+      <c r="C72" s="72"/>
+      <c r="D72" s="72"/>
+      <c r="E72" s="72"/>
+    </row>
+    <row r="73" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A73" s="72"/>
+      <c r="B73" s="72"/>
+      <c r="C73" s="72"/>
+      <c r="D73" s="72"/>
+      <c r="E73" s="72"/>
+    </row>
+    <row r="74" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A74" s="89" t="s">
+        <v>922</v>
+      </c>
+      <c r="B74" s="72"/>
+      <c r="C74" s="72"/>
+      <c r="D74" s="72"/>
+      <c r="E74" s="72"/>
+    </row>
+    <row r="75" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A75" s="89" t="s">
+        <v>923</v>
+      </c>
+      <c r="B75" s="72"/>
+      <c r="C75" s="72"/>
+      <c r="D75" s="72"/>
+      <c r="E75" s="72"/>
+    </row>
+    <row r="76" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A76" s="74" t="s">
+        <v>994</v>
+      </c>
+      <c r="B76" s="72"/>
+      <c r="C76" s="72"/>
+      <c r="D76" s="72"/>
+      <c r="E76" s="72"/>
+    </row>
+    <row r="77" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A77" s="72" t="s">
+        <v>979</v>
+      </c>
+      <c r="B77" s="72"/>
+      <c r="C77" s="72"/>
+      <c r="D77" s="72"/>
+      <c r="E77" s="72"/>
+    </row>
+    <row r="78" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A78" s="72" t="s">
+        <v>980</v>
+      </c>
+      <c r="B78" s="72"/>
+      <c r="C78" s="72"/>
+      <c r="D78" s="72"/>
+      <c r="E78" s="72"/>
+    </row>
+    <row r="79" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A79" s="72" t="s">
+        <v>981</v>
+      </c>
+      <c r="B79" s="72"/>
+      <c r="C79" s="72"/>
+      <c r="D79" s="72"/>
+      <c r="E79" s="72"/>
+    </row>
+    <row r="80" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A80" s="72" t="s">
+        <v>982</v>
+      </c>
+      <c r="B80" s="72"/>
+      <c r="C80" s="72"/>
+      <c r="D80" s="72"/>
+      <c r="E80" s="72"/>
+    </row>
+    <row r="81" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A81" s="72" t="s">
+        <v>980</v>
+      </c>
+      <c r="B81" s="72"/>
+      <c r="C81" s="72"/>
+      <c r="D81" s="72"/>
+      <c r="E81" s="72"/>
+    </row>
+    <row r="82" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A82" s="72" t="s">
+        <v>981</v>
+      </c>
+      <c r="B82" s="72"/>
+      <c r="C82" s="72"/>
+      <c r="D82" s="72"/>
+      <c r="E82" s="72"/>
+    </row>
+    <row r="83" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A83" s="74" t="s">
+        <v>924</v>
+      </c>
+      <c r="B83" s="72"/>
+      <c r="C83" s="72"/>
+      <c r="D83" s="72"/>
+      <c r="E83" s="72"/>
+    </row>
+    <row r="84" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A84" s="75"/>
+      <c r="B84" s="72"/>
+      <c r="C84" s="72"/>
+      <c r="D84" s="72"/>
+      <c r="E84" s="72"/>
+    </row>
+    <row r="85" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A85" s="75" t="s">
+        <v>925</v>
+      </c>
+      <c r="B85" s="72"/>
+      <c r="C85" s="72"/>
+      <c r="D85" s="72"/>
+      <c r="E85" s="72"/>
+    </row>
+    <row r="86" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A86" s="75" t="s">
+        <v>926</v>
+      </c>
+      <c r="B86" s="72"/>
+      <c r="C86" s="72"/>
+      <c r="D86" s="72"/>
+      <c r="E86" s="72"/>
+    </row>
+    <row r="87" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A87" s="75" t="s">
+        <v>927</v>
+      </c>
+      <c r="B87" s="72"/>
+      <c r="C87" s="72"/>
+      <c r="D87" s="72"/>
+      <c r="E87" s="72"/>
+    </row>
+    <row r="88" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A88" s="74"/>
+      <c r="B88" s="72"/>
+      <c r="C88" s="72"/>
+      <c r="D88" s="72"/>
+      <c r="E88" s="72"/>
+    </row>
+    <row r="89" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A89" s="89" t="s">
+        <v>928</v>
+      </c>
+      <c r="B89" s="72"/>
+      <c r="C89" s="72"/>
+      <c r="D89" s="72"/>
+      <c r="E89" s="72"/>
+    </row>
+    <row r="90" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A90" s="72" t="s">
+        <v>929</v>
+      </c>
+      <c r="B90" s="72"/>
+      <c r="C90" s="72"/>
+      <c r="D90" s="72"/>
+      <c r="E90" s="72"/>
+    </row>
+    <row r="91" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A91" s="72" t="s">
+        <v>930</v>
+      </c>
+      <c r="B91" s="72"/>
+      <c r="C91" s="72"/>
+      <c r="D91" s="72"/>
+      <c r="E91" s="72"/>
+    </row>
+    <row r="92" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A92" s="72" t="s">
+        <v>931</v>
+      </c>
+      <c r="B92" s="72"/>
+      <c r="C92" s="72"/>
+      <c r="D92" s="72"/>
+      <c r="E92" s="72"/>
+    </row>
+    <row r="93" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A93" s="74" t="s">
+        <v>932</v>
+      </c>
+      <c r="B93" s="72"/>
+      <c r="C93" s="72"/>
+      <c r="D93" s="72"/>
+      <c r="E93" s="72"/>
+    </row>
+    <row r="94" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A94" s="74" t="s">
+        <v>924</v>
+      </c>
+      <c r="B94" s="72"/>
+      <c r="C94" s="72"/>
+      <c r="D94" s="72"/>
+      <c r="E94" s="72"/>
+    </row>
+    <row r="95" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A95" s="75"/>
+      <c r="B95" s="72"/>
+      <c r="C95" s="72"/>
+      <c r="D95" s="72"/>
+      <c r="E95" s="72"/>
+    </row>
+    <row r="96" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A96" s="75" t="s">
+        <v>933</v>
+      </c>
+      <c r="B96" s="72"/>
+      <c r="C96" s="72"/>
+      <c r="D96" s="72"/>
+      <c r="E96" s="72"/>
+    </row>
+    <row r="97" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A97" s="75" t="s">
+        <v>934</v>
+      </c>
+      <c r="B97" s="72"/>
+      <c r="C97" s="72"/>
+      <c r="D97" s="72"/>
+      <c r="E97" s="72"/>
+    </row>
+    <row r="98" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A98" s="74"/>
+      <c r="B98" s="72"/>
+      <c r="C98" s="72"/>
+      <c r="D98" s="72"/>
+      <c r="E98" s="72"/>
+    </row>
+    <row r="99" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A99" s="72"/>
+      <c r="B99" s="72"/>
+      <c r="C99" s="72"/>
+      <c r="D99" s="72"/>
+      <c r="E99" s="72"/>
+    </row>
+    <row r="100" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A100" s="89" t="s">
+        <v>935</v>
+      </c>
+      <c r="B100" s="72"/>
+      <c r="C100" s="72"/>
+      <c r="D100" s="72"/>
+      <c r="E100" s="72"/>
+    </row>
+    <row r="101" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A101" s="91" t="s">
+        <v>936</v>
+      </c>
+      <c r="B101" s="91" t="s">
+        <v>658</v>
+      </c>
+      <c r="C101" s="91" t="s">
+        <v>937</v>
+      </c>
+      <c r="D101" s="92" t="s">
+        <v>851</v>
+      </c>
+      <c r="E101" s="72"/>
+    </row>
+    <row r="102" spans="1:5" s="90" customFormat="1" ht="83.25" thickBot="1">
+      <c r="A102" s="79">
+        <v>1</v>
+      </c>
+      <c r="B102" s="79" t="s">
+        <v>938</v>
+      </c>
+      <c r="C102" s="79" t="s">
+        <v>939</v>
+      </c>
+      <c r="D102" s="93" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E102" s="72"/>
+    </row>
+    <row r="103" spans="1:5" s="90" customFormat="1" ht="33.75" thickBot="1">
+      <c r="A103" s="79">
+        <v>2</v>
+      </c>
+      <c r="B103" s="79" t="s">
+        <v>940</v>
+      </c>
+      <c r="C103" s="79" t="s">
+        <v>939</v>
+      </c>
+      <c r="D103" s="93" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E103" s="72"/>
+    </row>
+    <row r="104" spans="1:5" s="90" customFormat="1" ht="33.75" thickBot="1">
+      <c r="A104" s="79">
+        <v>3</v>
+      </c>
+      <c r="B104" s="79" t="s">
+        <v>941</v>
+      </c>
+      <c r="C104" s="79" t="s">
+        <v>939</v>
+      </c>
+      <c r="D104" s="81" t="s">
+        <v>942</v>
+      </c>
+      <c r="E104" s="72"/>
+    </row>
+    <row r="105" spans="1:5" s="90" customFormat="1" ht="20.25" thickBot="1">
+      <c r="A105" s="79">
+        <v>4</v>
+      </c>
+      <c r="B105" s="79" t="s">
+        <v>943</v>
+      </c>
+      <c r="C105" s="79" t="s">
+        <v>510</v>
+      </c>
+      <c r="D105" s="81" t="s">
+        <v>510</v>
+      </c>
+      <c r="E105" s="72"/>
+    </row>
+    <row r="106" spans="1:5" s="90" customFormat="1" ht="66.75" thickBot="1">
+      <c r="A106" s="79">
+        <v>5</v>
+      </c>
+      <c r="B106" s="79" t="s">
+        <v>944</v>
+      </c>
+      <c r="C106" s="79" t="s">
+        <v>939</v>
+      </c>
+      <c r="D106" s="93" t="s">
+        <v>945</v>
+      </c>
+      <c r="E106" s="72"/>
+    </row>
+    <row r="107" spans="1:5" s="90" customFormat="1" ht="66.75" thickBot="1">
+      <c r="A107" s="79">
+        <v>6</v>
+      </c>
+      <c r="B107" s="79" t="s">
+        <v>946</v>
+      </c>
+      <c r="C107" s="79" t="s">
+        <v>939</v>
+      </c>
+      <c r="D107" s="81" t="s">
+        <v>947</v>
+      </c>
+      <c r="E107" s="72"/>
+    </row>
+    <row r="108" spans="1:5" s="90" customFormat="1" ht="33.75" thickBot="1">
+      <c r="A108" s="79">
+        <v>7</v>
+      </c>
+      <c r="B108" s="79" t="s">
+        <v>948</v>
+      </c>
+      <c r="C108" s="79" t="s">
+        <v>939</v>
+      </c>
+      <c r="D108" s="81" t="s">
+        <v>942</v>
+      </c>
+      <c r="E108" s="72"/>
+    </row>
+    <row r="109" spans="1:5" s="90" customFormat="1" ht="33.75" thickBot="1">
+      <c r="A109" s="79">
+        <v>8</v>
+      </c>
+      <c r="B109" s="79" t="s">
+        <v>949</v>
+      </c>
+      <c r="C109" s="79" t="s">
+        <v>939</v>
+      </c>
+      <c r="D109" s="81" t="s">
+        <v>942</v>
+      </c>
+      <c r="E109" s="72"/>
+    </row>
+    <row r="110" spans="1:5" s="90" customFormat="1" ht="33.75" thickBot="1">
+      <c r="A110" s="79" t="s">
+        <v>950</v>
+      </c>
+      <c r="B110" s="79" t="s">
+        <v>951</v>
+      </c>
+      <c r="C110" s="79" t="s">
+        <v>939</v>
+      </c>
+      <c r="D110" s="93" t="s">
+        <v>952</v>
+      </c>
+      <c r="E110" s="72"/>
+    </row>
+    <row r="111" spans="1:5" s="90" customFormat="1" ht="66.75" thickBot="1">
+      <c r="A111" s="79" t="s">
+        <v>953</v>
+      </c>
+      <c r="B111" s="79" t="s">
+        <v>954</v>
+      </c>
+      <c r="C111" s="79" t="s">
+        <v>939</v>
+      </c>
+      <c r="D111" s="93" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E111" s="72"/>
+    </row>
+    <row r="112" spans="1:5" s="90" customFormat="1" ht="66">
+      <c r="A112" s="79" t="s">
+        <v>955</v>
+      </c>
+      <c r="B112" s="79" t="s">
+        <v>956</v>
+      </c>
+      <c r="C112" s="79" t="s">
+        <v>939</v>
+      </c>
+      <c r="D112" s="89" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E112" s="72"/>
+    </row>
+    <row r="113" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A113" s="89" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B113" s="72"/>
+      <c r="C113" s="72"/>
+      <c r="D113" s="72"/>
+      <c r="E113" s="72"/>
+    </row>
+    <row r="114" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A114" s="75"/>
+      <c r="B114" s="72"/>
+      <c r="C114" s="72"/>
+      <c r="D114" s="72"/>
+      <c r="E114" s="72"/>
+    </row>
+    <row r="115" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A115" s="95" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B115" s="72"/>
+      <c r="C115" s="72"/>
+      <c r="D115" s="72"/>
+      <c r="E115" s="72"/>
+    </row>
+    <row r="116" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A116" s="95" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B116" s="72"/>
+      <c r="C116" s="72"/>
+      <c r="D116" s="72"/>
+      <c r="E116" s="72"/>
+    </row>
+    <row r="117" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A117" s="74"/>
+      <c r="B117" s="72"/>
+      <c r="C117" s="72"/>
+      <c r="D117" s="72"/>
+      <c r="E117" s="72"/>
+    </row>
+    <row r="118" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A118" s="74" t="s">
+        <v>957</v>
+      </c>
+      <c r="B118" s="72"/>
+      <c r="C118" s="72"/>
+      <c r="D118" s="72"/>
+      <c r="E118" s="72"/>
+    </row>
+    <row r="119" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A119" s="74" t="s">
+        <v>958</v>
+      </c>
+      <c r="B119" s="72"/>
+      <c r="C119" s="72"/>
+      <c r="D119" s="72"/>
+      <c r="E119" s="72"/>
+    </row>
+    <row r="120" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A120" s="74" t="s">
+        <v>958</v>
+      </c>
+      <c r="B120" s="72"/>
+      <c r="C120" s="72"/>
+      <c r="D120" s="72"/>
+      <c r="E120" s="72"/>
+    </row>
+    <row r="121" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A121" s="74" t="s">
+        <v>959</v>
+      </c>
+      <c r="B121" s="72"/>
+      <c r="C121" s="72"/>
+      <c r="D121" s="72"/>
+      <c r="E121" s="72"/>
+    </row>
+    <row r="122" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A122" s="74" t="s">
+        <v>960</v>
+      </c>
+      <c r="B122" s="72"/>
+      <c r="C122" s="72"/>
+      <c r="D122" s="72"/>
+      <c r="E122" s="72"/>
+    </row>
+    <row r="123" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A123" s="74" t="s">
+        <v>961</v>
+      </c>
+      <c r="B123" s="72"/>
+      <c r="C123" s="72"/>
+      <c r="D123" s="72"/>
+      <c r="E123" s="72"/>
+    </row>
+    <row r="124" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A124" s="74" t="s">
+        <v>962</v>
+      </c>
+      <c r="B124" s="72"/>
+      <c r="C124" s="72"/>
+      <c r="D124" s="72"/>
+      <c r="E124" s="72"/>
+    </row>
+    <row r="125" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A125" s="74" t="s">
+        <v>963</v>
+      </c>
+      <c r="B125" s="72"/>
+      <c r="C125" s="72"/>
+      <c r="D125" s="72"/>
+      <c r="E125" s="72"/>
+    </row>
+    <row r="126" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A126" s="74" t="s">
+        <v>964</v>
+      </c>
+      <c r="B126" s="72"/>
+      <c r="C126" s="72"/>
+      <c r="D126" s="72"/>
+      <c r="E126" s="72"/>
+    </row>
+    <row r="127" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A127" s="74" t="s">
+        <v>965</v>
+      </c>
+      <c r="B127" s="72"/>
+      <c r="C127" s="72"/>
+      <c r="D127" s="72"/>
+      <c r="E127" s="72"/>
+    </row>
+    <row r="128" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A128" s="74" t="s">
+        <v>966</v>
+      </c>
+      <c r="B128" s="72"/>
+      <c r="C128" s="72"/>
+      <c r="D128" s="72"/>
+      <c r="E128" s="72"/>
+    </row>
+    <row r="129" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A129" s="74" t="s">
+        <v>838</v>
+      </c>
+      <c r="B129" s="72"/>
+      <c r="C129" s="72"/>
+      <c r="D129" s="72"/>
+      <c r="E129" s="72"/>
+    </row>
+    <row r="130" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A130" s="74" t="s">
+        <v>967</v>
+      </c>
+      <c r="B130" s="72"/>
+      <c r="C130" s="72"/>
+      <c r="D130" s="72"/>
+      <c r="E130" s="72"/>
+    </row>
+    <row r="131" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A131" s="74" t="s">
+        <v>968</v>
+      </c>
+      <c r="B131" s="72"/>
+      <c r="C131" s="72"/>
+      <c r="D131" s="72"/>
+      <c r="E131" s="72"/>
+    </row>
+    <row r="132" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A132" s="74" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B132" s="72"/>
+      <c r="C132" s="72"/>
+      <c r="D132" s="72"/>
+      <c r="E132" s="72"/>
+    </row>
+    <row r="133" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A133" s="89" t="s">
+        <v>969</v>
+      </c>
+      <c r="B133" s="72"/>
+      <c r="C133" s="72"/>
+      <c r="D133" s="72"/>
+      <c r="E133" s="72"/>
+    </row>
+    <row r="134" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A134" s="75"/>
+      <c r="B134" s="72"/>
+      <c r="C134" s="72"/>
+      <c r="D134" s="72"/>
+      <c r="E134" s="72"/>
+    </row>
+    <row r="135" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A135" s="95" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B135" s="72"/>
+      <c r="C135" s="72"/>
+      <c r="D135" s="72"/>
+      <c r="E135" s="72"/>
+    </row>
+    <row r="136" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A136" s="95" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B136" s="72"/>
+      <c r="C136" s="72"/>
+      <c r="D136" s="72"/>
+      <c r="E136" s="72"/>
+    </row>
+    <row r="137" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A137" s="75" t="s">
+        <v>970</v>
+      </c>
+      <c r="B137" s="72"/>
+      <c r="C137" s="72"/>
+      <c r="D137" s="72"/>
+      <c r="E137" s="72"/>
+    </row>
+    <row r="138" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A138" s="96" t="s">
+        <v>778</v>
+      </c>
+      <c r="B138" s="72"/>
+      <c r="C138" s="72"/>
+      <c r="D138" s="72"/>
+      <c r="E138" s="72"/>
+    </row>
+    <row r="139" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A139" s="96" t="s">
+        <v>625</v>
+      </c>
+      <c r="B139" s="72"/>
+      <c r="C139" s="72"/>
+      <c r="D139" s="72"/>
+      <c r="E139" s="72"/>
+    </row>
+    <row r="140" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A140" s="75" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B140" s="72"/>
+      <c r="C140" s="72"/>
+      <c r="D140" s="72"/>
+      <c r="E140" s="72"/>
+    </row>
+    <row r="141" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A141" s="75" t="s">
+        <v>971</v>
+      </c>
+      <c r="B141" s="72"/>
+      <c r="C141" s="72"/>
+      <c r="D141" s="72"/>
+      <c r="E141" s="72"/>
+    </row>
+    <row r="142" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A142" s="74"/>
+      <c r="B142" s="72"/>
+      <c r="C142" s="72"/>
+      <c r="D142" s="72"/>
+      <c r="E142" s="72"/>
+    </row>
+    <row r="143" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A143" s="74" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B143" s="72"/>
+      <c r="C143" s="72"/>
+      <c r="D143" s="72"/>
+      <c r="E143" s="72"/>
+    </row>
+    <row r="144" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A144" s="89" t="s">
+        <v>972</v>
+      </c>
+      <c r="B144" s="72"/>
+      <c r="C144" s="72"/>
+      <c r="D144" s="72"/>
+      <c r="E144" s="72"/>
+    </row>
+    <row r="145" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A145" s="74" t="s">
+        <v>995</v>
+      </c>
+      <c r="B145" s="72"/>
+      <c r="C145" s="72"/>
+      <c r="D145" s="72"/>
+      <c r="E145" s="72"/>
+    </row>
+    <row r="146" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A146" s="91" t="s">
+        <v>973</v>
+      </c>
+      <c r="B146" s="92" t="s">
+        <v>974</v>
+      </c>
+      <c r="C146" s="72"/>
+      <c r="D146" s="72"/>
+      <c r="E146" s="72"/>
+    </row>
+    <row r="147" spans="1:5" s="90" customFormat="1" ht="33.75" thickBot="1">
+      <c r="A147" s="79" t="s">
+        <v>975</v>
+      </c>
+      <c r="B147" s="81" t="s">
+        <v>976</v>
+      </c>
+      <c r="C147" s="72"/>
+      <c r="D147" s="72"/>
+      <c r="E147" s="72"/>
+    </row>
+    <row r="148" spans="1:5" s="90" customFormat="1" ht="19.5">
+      <c r="A148" s="79" t="s">
+        <v>977</v>
+      </c>
+      <c r="B148" s="74" t="s">
+        <v>978</v>
+      </c>
+      <c r="C148" s="72"/>
+      <c r="D148" s="72"/>
+      <c r="E148" s="72"/>
+    </row>
+    <row r="149" spans="1:5" s="90" customFormat="1" ht="33">
+      <c r="A149" s="74" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B149" s="72"/>
+      <c r="C149" s="72"/>
+      <c r="D149" s="72"/>
+      <c r="E149" s="72"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D8638F-2AD2-4098-8321-0BD962A63380}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/PCBNo.10081/FPGA/修正履歴.xlsx
+++ b/PCBNo.10081/FPGA/修正履歴.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FPGA work\PCBNo.10081\FPGA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FPGAwork\PCBNo.10081\FPGA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F38BC98-97EE-4E89-B636-CBEA2B7A2410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F9C9D21-DD22-4B18-A0AA-A38AAE8BFBBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{3A2BB469-6CC5-41C3-8C98-63503D4CF60C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="11" xr2:uid="{3A2BB469-6CC5-41C3-8C98-63503D4CF60C}"/>
   </bookViews>
   <sheets>
     <sheet name="修正履歴" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="1021">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="1054">
   <si>
     <t>No</t>
     <phoneticPr fontId="1"/>
@@ -7218,18 +7218,380 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>No1~10の確認</t>
-    <rPh sb="7" eb="9">
+    <t>No.1~10の確認</t>
+    <rPh sb="8" eb="10">
       <t>カクニン</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>修正サマリ（6ファイル）</t>
+  </si>
+  <si>
+    <t>修正1: [致命的] FDCクロック定義のネット名修正 (MT548/MT420/MT446/MT447)</t>
+  </si>
+  <si>
+    <t>クロック定義を全削除（コメントのみに）</t>
+  </si>
+  <si>
+    <t>修正2: [中] RTLレベル syn_preserve 属性修正 (BN105/CL190/BN132)</t>
+  </si>
+  <si>
+    <t>LEDLT_TOP.vhd</t>
+  </si>
+  <si>
+    <t>slv_ctrl_top.vhd</t>
+  </si>
+  <si>
+    <t>dec6b_5b.vhd</t>
+  </si>
+  <si>
+    <t>7E, 7J, 7K, 7M の重複FDCエントリを削除</t>
+  </si>
+  <si>
+    <t>修正3: [低] encoder組合せループ警告抑制 (BN161)</t>
+  </si>
+  <si>
+    <t>encoder_2bit.vhd</t>
+  </si>
+  <si>
+    <t>全体期待効果</t>
+  </si>
+  <si>
+    <t>修正後（期待）</t>
+  </si>
+  <si>
+    <t>216件</t>
+  </si>
+  <si>
+    <t>MT548/MT420/MT529</t>
+  </si>
+  <si>
+    <t>12件</t>
+  </si>
+  <si>
+    <t>0件</t>
+  </si>
+  <si>
+    <t>BN105</t>
+  </si>
+  <si>
+    <t>27件</t>
+  </si>
+  <si>
+    <t>BN161</t>
+  </si>
+  <si>
+    <t>100件</t>
+  </si>
+  <si>
+    <t>CL190 (s_LEDPTN/s_prpty)</t>
+  </si>
+  <si>
+    <t>BN132 (DATAOUT)</t>
+  </si>
+  <si>
+    <t>6件</t>
+  </si>
+  <si>
+    <r>
+      <t>Section 0 としてクロック定義を追加。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>{n:CLKOP_t}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>{n:slv_com_top_inst.clk_gen_inst2.PLL_inst.CLKCOM_OUT}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> 等の階層パスに変更</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>期待効果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: MT548×4、MT420×4、MT529×4、MT447×8、MT446×6 の合計 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>26件のワーニングが解消</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> され、Synplifyレベルで全PLLクロックが同一グループ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>pll_clks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> に配置。MULTICYCLE/FALSE_PATH制約も正常に適用。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>syn_keep</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>syn_preserve</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> (s_LEDPTN)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>syn_keep</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>syn_preserve</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> (s_prpty)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>syn_preserve of DATAOUT : port</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> を追加</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>期待効果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: BN105×27件が解消。CL190のs_LEDPTN×6、s_prpty×6、BN132のDATAOUT×6 も解消見込み（合計 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>最大45件削減</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>attribute syn_loopcheck of RTL : architecture is false;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> を追加</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>期待効果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: BN161×100件が解消見込み。FDCの </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>syn_loopcheck {0}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> もバックアップとして維持。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>~45件</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>（IPコア起因17件含む）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>次のステップ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: Diamond 3.14で </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>Clean → Synthesize Design → 全フロー再実行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> してください。合成からやり直すことで、全修正がSRR/TWRに反映されます。</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="32">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7458,6 +7820,36 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <name val="メイリオ"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="メイリオ"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="13.5"/>
+      <name val="メイリオ"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="メイリオ"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="メイリオ"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -7523,7 +7915,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7814,6 +8206,45 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10567,10 +10998,216 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D8638F-2AD2-4098-8321-0BD962A63380}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A13442C-D3F5-44DA-A340-0A4C29B54C09}">
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="3" width="82.125" style="98" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="57">
+      <c r="A1" s="97" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="87">
+      <c r="A2" s="99" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="100" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="101" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="38.25" thickBot="1">
+      <c r="A4" s="102" t="s">
+        <v>693</v>
+      </c>
+      <c r="B4" s="103" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="72.75">
+      <c r="A5" s="102" t="s">
+        <v>659</v>
+      </c>
+      <c r="B5" s="104" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="131.25">
+      <c r="A6" s="105" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="65.25">
+      <c r="A7" s="99" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="100" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="101" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="19.5" thickBot="1">
+      <c r="A9" s="102" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B9" s="106" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="19.5" thickBot="1">
+      <c r="A10" s="102" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B10" s="106" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="19.5" thickBot="1">
+      <c r="A11" s="102" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B11" s="106" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="37.5">
+      <c r="A12" s="102" t="s">
+        <v>659</v>
+      </c>
+      <c r="B12" s="104" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="75">
+      <c r="A13" s="105" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="43.5">
+      <c r="A14" s="99" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="100" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="101" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="35.25">
+      <c r="A16" s="102" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B16" s="107" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="56.25">
+      <c r="A17" s="105" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="21.75">
+      <c r="A18" s="99" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="100" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" s="100" t="s">
+        <v>973</v>
+      </c>
+      <c r="C19" s="101" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="19.5" thickBot="1">
+      <c r="A20" s="108" t="s">
+        <v>846</v>
+      </c>
+      <c r="B20" s="108" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C20" s="109" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="19.5" thickBot="1">
+      <c r="A21" s="108" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B21" s="108" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C21" s="103" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="19.5" thickBot="1">
+      <c r="A22" s="108" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B22" s="108" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C22" s="103" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="19.5" thickBot="1">
+      <c r="A23" s="108" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B23" s="108" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C23" s="103" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="19.5" thickBot="1">
+      <c r="A24" s="108" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B24" s="108" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C24" s="103" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="108" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B25" s="108" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C25" s="104" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="93.75">
+      <c r="A26" s="105" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/PCBNo.10081/FPGA/修正履歴.xlsx
+++ b/PCBNo.10081/FPGA/修正履歴.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/512e22ffcc52695f/ドキュメント/GitHub/PCBNo.10081/PCBNo.10081/FPGA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_74A6D602E2D12DC3FCCEB9C6F2E12A7DDD73DFB7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13DA9D4A-5AE9-4E14-87DC-D993031AD00C}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="11_74A6D602E2D12DC3FCCEB9C6F2E12A7DDD73DFB7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B01EC08-44FF-40FB-BD34-EE3582D1A79D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="修正履歴" sheetId="1" r:id="rId1"/>
@@ -27,13 +27,14 @@
     <sheet name="No.11" sheetId="12" r:id="rId12"/>
     <sheet name="No.12" sheetId="13" r:id="rId13"/>
     <sheet name="No.13" sheetId="14" r:id="rId14"/>
+    <sheet name="No.14" sheetId="15" r:id="rId15"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="1158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="1182">
   <si>
     <t>No</t>
   </si>
@@ -3894,12 +3895,174 @@
       <t> が消えていれば成功です。</t>
     </r>
   </si>
+  <si>
+    <t>修正内容まとめ</t>
+  </si>
+  <si>
+    <t>SP0557_warning_list.xlsx の解析結果</t>
+  </si>
+  <si>
+    <t>1. SP0557.fdc（Synplify FDC制約ファイル）</t>
+  </si>
+  <si>
+    <t>修正前のパス</t>
+  </si>
+  <si>
+    <t>修正後のパス</t>
+  </si>
+  <si>
+    <t>...PLL_inst.CLKCOM_OUT</t>
+  </si>
+  <si>
+    <t>...PLL_inst.PLLInst_0.CLKOP</t>
+  </si>
+  <si>
+    <t>...PLL_inst.CLK2A</t>
+  </si>
+  <si>
+    <t>...PLL_inst.PLLInst_0.CLKOS</t>
+  </si>
+  <si>
+    <t>...PLL_inst.s_PLL_CLK20M</t>
+  </si>
+  <si>
+    <t>...PLL_inst.PLLInst_0.CLKOS2</t>
+  </si>
+  <si>
+    <t>...PLL_inst.CLK1</t>
+  </si>
+  <si>
+    <t>...PLL_inst.PLLInst_0.CLKOS3</t>
+  </si>
+  <si>
+    <t>2. SP0557.lpf（Lattice MAP制約ファイル）</t>
+  </si>
+  <si>
+    <t>CLK2は内部信号、ポート名はCLKCOM_OUT</t>
+  </si>
+  <si>
+    <t>slv_com_top_inst/CLK2A</t>
+  </si>
+  <si>
+    <t>内部信号は"/"セパレータ</t>
+  </si>
+  <si>
+    <r>
+      <t>ワーニングリストから</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>高重要度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>の問題を特定し、修正しました。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>根本原因</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: define_clockのネットパスがpll_genのラッパーポート名（CLKCOM_OUT, CLK2A, s_PLL_CLK20M, CLK1）を参照していたが、Synplifyはそれらを認識できなかった。実際のクロックソースはEHXPLLLプリミティブ（PLLInst_0）の出力ポート。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>解消されるワーニング</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: MT548(4件), MT529(4件), MF511(1件), MT420(4件), MT446(6件), MT447(12件) = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>計31件</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>根本原因</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: クロックネット名が合成後のデザインに存在しない名前を参照していた。PARレポートから実際のネット名を確認し修正。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>解消されるワーニング</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: FREQUENCY(2件), BLOCK PATH(8件), MULTICYCLE(4件) = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>計14件</t>
+    </r>
+  </si>
+  <si>
+    <t>14</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>残ったワーニングの修正</t>
+    <rPh sb="0" eb="1">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="50">
+  <fonts count="51">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4236,7 +4399,13 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="12"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="Meiryo UI"/>
       <family val="3"/>
       <charset val="128"/>
@@ -4306,7 +4475,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4701,6 +4870,27 @@
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5222,9 +5412,15 @@
       <c r="F17" s="26"/>
     </row>
     <row r="18" spans="3:6">
-      <c r="C18" s="26"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="27"/>
+      <c r="C18" s="26">
+        <v>14</v>
+      </c>
+      <c r="D18" s="29" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>1181</v>
+      </c>
       <c r="F18" s="26"/>
     </row>
     <row r="19" spans="3:6">
@@ -7902,7 +8098,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="108" thickBot="1">
+    <row r="8" spans="1:4" ht="48" thickBot="1">
       <c r="A8" s="7" t="s">
         <v>1088</v>
       </c>
@@ -7916,7 +8112,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="62.25" thickBot="1">
+    <row r="9" spans="1:4" ht="32.25" thickBot="1">
       <c r="A9" s="7" t="s">
         <v>1090</v>
       </c>
@@ -7930,7 +8126,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="46.5" thickBot="1">
+    <row r="10" spans="1:4" ht="32.25" thickBot="1">
       <c r="A10" s="7" t="s">
         <v>1090</v>
       </c>
@@ -7944,7 +8140,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="79.5" thickBot="1">
+    <row r="11" spans="1:4" ht="32.25" thickBot="1">
       <c r="A11" s="7" t="s">
         <v>1090</v>
       </c>
@@ -7958,7 +8154,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="63">
+    <row r="12" spans="1:4" ht="31.5">
       <c r="A12" s="7" t="s">
         <v>1095</v>
       </c>
@@ -7991,7 +8187,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="48" thickBot="1">
+    <row r="15" spans="1:4" ht="32.25" thickBot="1">
       <c r="A15" s="7" t="s">
         <v>1095</v>
       </c>
@@ -8005,7 +8201,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="63">
+    <row r="16" spans="1:4" ht="31.5">
       <c r="A16" s="7" t="s">
         <v>1100</v>
       </c>
@@ -8038,7 +8234,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="78.75">
+    <row r="19" spans="1:4" ht="47.25">
       <c r="A19" s="7" t="s">
         <v>1105</v>
       </c>
@@ -8170,7 +8366,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="47.25">
+    <row r="47" spans="1:4" ht="31.5">
       <c r="A47" s="127" t="s">
         <v>60</v>
       </c>
@@ -8337,6 +8533,164 @@
       <c r="A64" s="9" t="s">
         <v>1157</v>
       </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39270148-7B96-4F2C-8D27-58B8ABADA861}">
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultRowHeight="19.5"/>
+  <cols>
+    <col min="1" max="1" width="59" style="90" customWidth="1"/>
+    <col min="2" max="2" width="38.625" style="90" customWidth="1"/>
+    <col min="3" max="3" width="59.625" style="90" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="90"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="138" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="138" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="139" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B3" s="137"/>
+      <c r="C3" s="137"/>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="138" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B4" s="137"/>
+      <c r="C4" s="137"/>
+    </row>
+    <row r="5" spans="1:3" ht="66">
+      <c r="A5" s="138" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B5" s="137"/>
+      <c r="C5" s="137"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="140" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B6" s="141" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C6" s="137"/>
+    </row>
+    <row r="7" spans="1:3" ht="20.25" thickBot="1">
+      <c r="A7" s="142" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B7" s="143" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C7" s="137"/>
+    </row>
+    <row r="8" spans="1:3" ht="20.25" thickBot="1">
+      <c r="A8" s="142" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B8" s="143" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C8" s="137"/>
+    </row>
+    <row r="9" spans="1:3" ht="20.25" thickBot="1">
+      <c r="A9" s="142" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B9" s="143" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C9" s="137"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="142" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B10" s="139" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C10" s="137"/>
+    </row>
+    <row r="11" spans="1:3" ht="33">
+      <c r="A11" s="138" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B11" s="137"/>
+      <c r="C11" s="137"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="138" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B12" s="137"/>
+      <c r="C12" s="137"/>
+    </row>
+    <row r="13" spans="1:3" ht="33">
+      <c r="A13" s="138" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B13" s="137"/>
+      <c r="C13" s="137"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="140" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B14" s="140" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C14" s="141" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="20.25" thickBot="1">
+      <c r="A15" s="142" t="s">
+        <v>899</v>
+      </c>
+      <c r="B15" s="142" t="s">
+        <v>900</v>
+      </c>
+      <c r="C15" s="143" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="142" t="s">
+        <v>902</v>
+      </c>
+      <c r="B16" s="142" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C16" s="139" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="33">
+      <c r="A17" s="138" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B17" s="137"/>
+      <c r="C17" s="137"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
